--- a/Dataset_Descriptives/austria_media_trends_weekly.xlsx
+++ b/Dataset_Descriptives/austria_media_trends_weekly.xlsx
@@ -526,16 +526,16 @@
         <v>2</v>
       </c>
       <c r="G2" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H2" t="n">
-        <v>8.705753724203909</v>
+        <v>9.505736753899704</v>
       </c>
       <c r="I2" t="n">
-        <v>17.41150744840782</v>
+        <v>17.82325641356195</v>
       </c>
       <c r="J2" t="n">
-        <v>75.86442531091978</v>
+        <v>74.85767693696017</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -547,7 +547,7 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>6</v>
+        <v>5.962479784366577</v>
       </c>
     </row>
     <row r="3">
@@ -570,16 +570,16 @@
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H3" t="n">
-        <v>8.705753724203909</v>
+        <v>10.69395384813717</v>
       </c>
       <c r="I3" t="n">
-        <v>14.92414924149242</v>
+        <v>15.44682222508702</v>
       </c>
       <c r="J3" t="n">
-        <v>85.81385813858139</v>
+        <v>86.7398478793348</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -591,7 +591,7 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>5</v>
+        <v>4.968733153638814</v>
       </c>
     </row>
     <row r="4">
@@ -599,7 +599,7 @@
         <v>41651</v>
       </c>
       <c r="B4" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C4" t="n">
         <v>4</v>
@@ -614,16 +614,16 @@
         <v>2</v>
       </c>
       <c r="G4" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H4" t="n">
-        <v>8.705753724203909</v>
+        <v>8.317519659662242</v>
       </c>
       <c r="I4" t="n">
-        <v>13.68047013803471</v>
+        <v>14.25860513084956</v>
       </c>
       <c r="J4" t="n">
-        <v>88.30121634549678</v>
+        <v>90.30449916204719</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -635,7 +635,7 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>5</v>
+        <v>4.968733153638814</v>
       </c>
     </row>
     <row r="5">
@@ -643,7 +643,7 @@
         <v>41658</v>
       </c>
       <c r="B5" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C5" t="n">
         <v>4</v>
@@ -658,16 +658,16 @@
         <v>2</v>
       </c>
       <c r="G5" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H5" t="n">
-        <v>9.94943282766161</v>
+        <v>9.505736753899704</v>
       </c>
       <c r="I5" t="n">
-        <v>14.92414924149242</v>
+        <v>14.25860513084956</v>
       </c>
       <c r="J5" t="n">
-        <v>84.57017903512369</v>
+        <v>85.55163078509733</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -679,7 +679,7 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>5</v>
+        <v>4.968733153638814</v>
       </c>
     </row>
     <row r="6">
@@ -687,7 +687,7 @@
         <v>41665</v>
       </c>
       <c r="B6" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C6" t="n">
         <v>4</v>
@@ -702,16 +702,16 @@
         <v>2</v>
       </c>
       <c r="G6" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H6" t="n">
-        <v>9.94943282766161</v>
+        <v>10.69395384813717</v>
       </c>
       <c r="I6" t="n">
-        <v>14.92414924149242</v>
+        <v>15.44682222508702</v>
       </c>
       <c r="J6" t="n">
-        <v>80.83914172475059</v>
+        <v>83.17519659662241</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -723,7 +723,7 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>5</v>
+        <v>4.968733153638814</v>
       </c>
     </row>
     <row r="7">
@@ -731,7 +731,7 @@
         <v>41672</v>
       </c>
       <c r="B7" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C7" t="n">
         <v>4</v>
@@ -746,16 +746,16 @@
         <v>2</v>
       </c>
       <c r="G7" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H7" t="n">
-        <v>9.94943282766161</v>
+        <v>10.69395384813717</v>
       </c>
       <c r="I7" t="n">
-        <v>14.92414924149242</v>
+        <v>15.44682222508702</v>
       </c>
       <c r="J7" t="n">
-        <v>84.57017903512369</v>
+        <v>83.17519659662241</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -767,7 +767,7 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>5</v>
+        <v>4.968733153638814</v>
       </c>
     </row>
     <row r="8">
@@ -775,7 +775,7 @@
         <v>41679</v>
       </c>
       <c r="B8" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C8" t="n">
         <v>4</v>
@@ -790,16 +790,16 @@
         <v>2</v>
       </c>
       <c r="G8" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H8" t="n">
-        <v>8.705753724203909</v>
+        <v>9.505736753899704</v>
       </c>
       <c r="I8" t="n">
-        <v>16.16782834495012</v>
+        <v>15.44682222508702</v>
       </c>
       <c r="J8" t="n">
-        <v>83.32649993166598</v>
+        <v>86.7398478793348</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -811,7 +811,7 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>5</v>
+        <v>4.968733153638814</v>
       </c>
     </row>
     <row r="9">
@@ -819,7 +819,7 @@
         <v>41686</v>
       </c>
       <c r="B9" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C9" t="n">
         <v>4</v>
@@ -834,16 +834,16 @@
         <v>2</v>
       </c>
       <c r="G9" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H9" t="n">
-        <v>8.705753724203909</v>
+        <v>9.505736753899704</v>
       </c>
       <c r="I9" t="n">
-        <v>16.16782834495012</v>
+        <v>15.44682222508702</v>
       </c>
       <c r="J9" t="n">
-        <v>79.59546262129288</v>
+        <v>81.98697950238495</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -855,7 +855,7 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>5</v>
+        <v>4.968733153638814</v>
       </c>
     </row>
     <row r="10">
@@ -863,7 +863,7 @@
         <v>41693</v>
       </c>
       <c r="B10" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C10" t="n">
         <v>4</v>
@@ -878,16 +878,16 @@
         <v>2</v>
       </c>
       <c r="G10" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H10" t="n">
-        <v>8.705753724203909</v>
+        <v>9.505736753899704</v>
       </c>
       <c r="I10" t="n">
-        <v>13.68047013803471</v>
+        <v>13.07038803661209</v>
       </c>
       <c r="J10" t="n">
-        <v>83.32649993166598</v>
+        <v>81.98697950238495</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -899,7 +899,7 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>5</v>
+        <v>4.968733153638814</v>
       </c>
     </row>
     <row r="11">
@@ -907,7 +907,7 @@
         <v>41700</v>
       </c>
       <c r="B11" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C11" t="n">
         <v>5</v>
@@ -922,16 +922,16 @@
         <v>2</v>
       </c>
       <c r="G11" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H11" t="n">
-        <v>9.94943282766161</v>
+        <v>9.505736753899704</v>
       </c>
       <c r="I11" t="n">
-        <v>14.92414924149242</v>
+        <v>15.44682222508702</v>
       </c>
       <c r="J11" t="n">
-        <v>80.83914172475059</v>
+        <v>83.17519659662241</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>4</v>
+        <v>3.974986522911051</v>
       </c>
     </row>
     <row r="12">
@@ -951,7 +951,7 @@
         <v>41707</v>
       </c>
       <c r="B12" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C12" t="n">
         <v>4</v>
@@ -966,16 +966,16 @@
         <v>2</v>
       </c>
       <c r="G12" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H12" t="n">
-        <v>8.705753724203909</v>
+        <v>9.505736753899704</v>
       </c>
       <c r="I12" t="n">
-        <v>14.92414924149242</v>
+        <v>15.44682222508702</v>
       </c>
       <c r="J12" t="n">
-        <v>80.83914172475059</v>
+        <v>85.55163078509733</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -987,7 +987,7 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>4</v>
+        <v>3.974986522911051</v>
       </c>
     </row>
     <row r="13">
@@ -995,7 +995,7 @@
         <v>41714</v>
       </c>
       <c r="B13" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C13" t="n">
         <v>4</v>
@@ -1010,16 +1010,16 @@
         <v>2</v>
       </c>
       <c r="G13" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H13" t="n">
-        <v>8.705753724203909</v>
+        <v>9.505736753899704</v>
       </c>
       <c r="I13" t="n">
-        <v>14.92414924149242</v>
+        <v>15.44682222508702</v>
       </c>
       <c r="J13" t="n">
-        <v>83.32649993166598</v>
+        <v>90.30449916204719</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1031,7 +1031,7 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>4</v>
+        <v>3.974986522911051</v>
       </c>
     </row>
     <row r="14">
@@ -1054,16 +1054,16 @@
         <v>2</v>
       </c>
       <c r="G14" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H14" t="n">
-        <v>8.705753724203909</v>
+        <v>8.317519659662242</v>
       </c>
       <c r="I14" t="n">
-        <v>14.92414924149242</v>
+        <v>15.44682222508702</v>
       </c>
       <c r="J14" t="n">
-        <v>83.32649993166598</v>
+        <v>84.36341369085987</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1075,7 +1075,7 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>4</v>
+        <v>3.974986522911051</v>
       </c>
     </row>
     <row r="15">
@@ -1083,7 +1083,7 @@
         <v>41728</v>
       </c>
       <c r="B15" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C15" t="n">
         <v>4</v>
@@ -1098,16 +1098,16 @@
         <v>2</v>
       </c>
       <c r="G15" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H15" t="n">
-        <v>8.705753724203909</v>
+        <v>9.505736753899704</v>
       </c>
       <c r="I15" t="n">
-        <v>13.68047013803471</v>
+        <v>13.07038803661209</v>
       </c>
       <c r="J15" t="n">
-        <v>84.57017903512369</v>
+        <v>84.36341369085987</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -1119,7 +1119,7 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>4</v>
+        <v>3.974986522911051</v>
       </c>
     </row>
     <row r="16">
@@ -1127,7 +1127,7 @@
         <v>41735</v>
       </c>
       <c r="B16" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C16" t="n">
         <v>4</v>
@@ -1142,16 +1142,16 @@
         <v>2</v>
       </c>
       <c r="G16" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H16" t="n">
-        <v>8.705753724203909</v>
+        <v>9.505736753899704</v>
       </c>
       <c r="I16" t="n">
-        <v>14.92414924149242</v>
+        <v>15.44682222508702</v>
       </c>
       <c r="J16" t="n">
-        <v>83.32649993166598</v>
+        <v>87.92806497357226</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -1163,7 +1163,7 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>4</v>
+        <v>3.974986522911051</v>
       </c>
     </row>
     <row r="17">
@@ -1171,7 +1171,7 @@
         <v>41742</v>
       </c>
       <c r="B17" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C17" t="n">
         <v>4</v>
@@ -1186,16 +1186,16 @@
         <v>2</v>
       </c>
       <c r="G17" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H17" t="n">
-        <v>8.705753724203909</v>
+        <v>9.505736753899704</v>
       </c>
       <c r="I17" t="n">
-        <v>16.16782834495012</v>
+        <v>16.63503931932448</v>
       </c>
       <c r="J17" t="n">
-        <v>80.83914172475059</v>
+        <v>83.17519659662241</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1207,7 +1207,7 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>4</v>
+        <v>3.974986522911051</v>
       </c>
     </row>
     <row r="18">
@@ -1230,16 +1230,16 @@
         <v>2</v>
       </c>
       <c r="G18" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H18" t="n">
-        <v>8.705753724203909</v>
+        <v>8.317519659662242</v>
       </c>
       <c r="I18" t="n">
-        <v>17.41150744840782</v>
+        <v>17.82325641356195</v>
       </c>
       <c r="J18" t="n">
-        <v>80.83914172475059</v>
+        <v>83.17519659662241</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -1251,7 +1251,7 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>4</v>
+        <v>3.974986522911051</v>
       </c>
     </row>
     <row r="19">
@@ -1259,7 +1259,7 @@
         <v>41756</v>
       </c>
       <c r="B19" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C19" t="n">
         <v>4</v>
@@ -1274,16 +1274,16 @@
         <v>2</v>
       </c>
       <c r="G19" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H19" t="n">
-        <v>8.705753724203909</v>
+        <v>8.317519659662242</v>
       </c>
       <c r="I19" t="n">
-        <v>17.41150744840782</v>
+        <v>17.82325641356195</v>
       </c>
       <c r="J19" t="n">
-        <v>79.59546262129288</v>
+        <v>80.79876240814748</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -1295,7 +1295,7 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>4</v>
+        <v>3.974986522911051</v>
       </c>
     </row>
     <row r="20">
@@ -1318,16 +1318,16 @@
         <v>2</v>
       </c>
       <c r="G20" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H20" t="n">
-        <v>7.462074620746208</v>
+        <v>8.317519659662242</v>
       </c>
       <c r="I20" t="n">
-        <v>13.68047013803471</v>
+        <v>13.07038803661209</v>
       </c>
       <c r="J20" t="n">
-        <v>83.32649993166598</v>
+        <v>86.7398478793348</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -1339,7 +1339,7 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>4</v>
+        <v>3.974986522911051</v>
       </c>
     </row>
     <row r="21">
@@ -1347,7 +1347,7 @@
         <v>41770</v>
       </c>
       <c r="B21" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C21" t="n">
         <v>4</v>
@@ -1362,16 +1362,16 @@
         <v>2</v>
       </c>
       <c r="G21" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H21" t="n">
-        <v>8.705753724203909</v>
+        <v>9.505736753899704</v>
       </c>
       <c r="I21" t="n">
-        <v>16.16782834495012</v>
+        <v>16.63503931932448</v>
       </c>
       <c r="J21" t="n">
-        <v>88.30121634549678</v>
+        <v>86.7398478793348</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -1383,7 +1383,7 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>4</v>
+        <v>3.974986522911051</v>
       </c>
     </row>
     <row r="22">
@@ -1391,7 +1391,7 @@
         <v>41777</v>
       </c>
       <c r="B22" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C22" t="n">
         <v>4</v>
@@ -1406,16 +1406,16 @@
         <v>2</v>
       </c>
       <c r="G22" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H22" t="n">
-        <v>8.705753724203909</v>
+        <v>9.505736753899704</v>
       </c>
       <c r="I22" t="n">
-        <v>14.92414924149242</v>
+        <v>15.44682222508702</v>
       </c>
       <c r="J22" t="n">
-        <v>85.81385813858139</v>
+        <v>86.7398478793348</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -1427,7 +1427,7 @@
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>3</v>
+        <v>3.974986522911051</v>
       </c>
     </row>
     <row r="23">
@@ -1435,7 +1435,7 @@
         <v>41784</v>
       </c>
       <c r="B23" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C23" t="n">
         <v>4</v>
@@ -1450,16 +1450,16 @@
         <v>2</v>
       </c>
       <c r="G23" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H23" t="n">
-        <v>8.705753724203909</v>
+        <v>9.505736753899704</v>
       </c>
       <c r="I23" t="n">
-        <v>16.16782834495012</v>
+        <v>16.63503931932448</v>
       </c>
       <c r="J23" t="n">
-        <v>94.5196118627853</v>
+        <v>97.43380172747197</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -1471,7 +1471,7 @@
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>4</v>
+        <v>3.974986522911051</v>
       </c>
     </row>
     <row r="24">
@@ -1479,7 +1479,7 @@
         <v>41791</v>
       </c>
       <c r="B24" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C24" t="n">
         <v>4</v>
@@ -1488,22 +1488,22 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F24" t="n">
         <v>2</v>
       </c>
       <c r="G24" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H24" t="n">
-        <v>8.705753724203909</v>
+        <v>8.317519659662242</v>
       </c>
       <c r="I24" t="n">
-        <v>13.68047013803471</v>
+        <v>11.88217094237463</v>
       </c>
       <c r="J24" t="n">
-        <v>87.05753724203909</v>
+        <v>85.55163078509733</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -1515,7 +1515,7 @@
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>4</v>
+        <v>3.974986522911051</v>
       </c>
     </row>
     <row r="25">
@@ -1523,7 +1523,7 @@
         <v>41798</v>
       </c>
       <c r="B25" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C25" t="n">
         <v>4</v>
@@ -1538,16 +1538,16 @@
         <v>2</v>
       </c>
       <c r="G25" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H25" t="n">
-        <v>8.705753724203909</v>
+        <v>9.505736753899704</v>
       </c>
       <c r="I25" t="n">
-        <v>17.41150744840782</v>
+        <v>16.63503931932448</v>
       </c>
       <c r="J25" t="n">
-        <v>79.59546262129288</v>
+        <v>80.79876240814748</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -1559,7 +1559,7 @@
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>3</v>
+        <v>3.974986522911051</v>
       </c>
     </row>
     <row r="26">
@@ -1567,7 +1567,7 @@
         <v>41805</v>
       </c>
       <c r="B26" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C26" t="n">
         <v>4</v>
@@ -1582,16 +1582,16 @@
         <v>2</v>
       </c>
       <c r="G26" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H26" t="n">
-        <v>9.94943282766161</v>
+        <v>8.317519659662242</v>
       </c>
       <c r="I26" t="n">
-        <v>21.14254475878092</v>
+        <v>19.01147350779941</v>
       </c>
       <c r="J26" t="n">
-        <v>77.10810441437748</v>
+        <v>79.61054531391002</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -1603,7 +1603,7 @@
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>3</v>
+        <v>2.981239892183289</v>
       </c>
     </row>
     <row r="27">
@@ -1626,16 +1626,16 @@
         <v>2</v>
       </c>
       <c r="G27" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H27" t="n">
-        <v>8.705753724203909</v>
+        <v>9.505736753899704</v>
       </c>
       <c r="I27" t="n">
-        <v>18.65518655186552</v>
+        <v>17.82325641356195</v>
       </c>
       <c r="J27" t="n">
-        <v>79.59546262129288</v>
+        <v>81.98697950238495</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -1647,7 +1647,7 @@
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>3</v>
+        <v>2.981239892183289</v>
       </c>
     </row>
     <row r="28">
@@ -1655,7 +1655,7 @@
         <v>41819</v>
       </c>
       <c r="B28" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C28" t="n">
         <v>4</v>
@@ -1670,16 +1670,16 @@
         <v>2</v>
       </c>
       <c r="G28" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H28" t="n">
-        <v>9.94943282766161</v>
+        <v>9.505736753899704</v>
       </c>
       <c r="I28" t="n">
-        <v>17.41150744840782</v>
+        <v>17.82325641356195</v>
       </c>
       <c r="J28" t="n">
-        <v>79.59546262129288</v>
+        <v>78.42232821967256</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -1691,7 +1691,7 @@
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>3</v>
+        <v>2.981239892183289</v>
       </c>
     </row>
     <row r="29">
@@ -1699,7 +1699,7 @@
         <v>41826</v>
       </c>
       <c r="B29" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C29" t="n">
         <v>4</v>
@@ -1714,16 +1714,16 @@
         <v>2</v>
       </c>
       <c r="G29" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H29" t="n">
-        <v>8.705753724203909</v>
+        <v>10.69395384813717</v>
       </c>
       <c r="I29" t="n">
-        <v>18.65518655186552</v>
+        <v>19.01147350779941</v>
       </c>
       <c r="J29" t="n">
-        <v>83.32649993166598</v>
+        <v>80.79876240814748</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -1735,7 +1735,7 @@
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>4</v>
+        <v>3.974986522911051</v>
       </c>
     </row>
     <row r="30">
@@ -1758,16 +1758,16 @@
         <v>2</v>
       </c>
       <c r="G30" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H30" t="n">
-        <v>8.705753724203909</v>
+        <v>9.505736753899704</v>
       </c>
       <c r="I30" t="n">
-        <v>13.68047013803471</v>
+        <v>14.25860513084956</v>
       </c>
       <c r="J30" t="n">
-        <v>78.35178351783517</v>
+        <v>81.98697950238495</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -1779,7 +1779,7 @@
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>4</v>
+        <v>3.974986522911051</v>
       </c>
     </row>
     <row r="31">
@@ -1787,7 +1787,7 @@
         <v>41840</v>
       </c>
       <c r="B31" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C31" t="n">
         <v>4</v>
@@ -1802,16 +1802,16 @@
         <v>2</v>
       </c>
       <c r="G31" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H31" t="n">
-        <v>9.94943282766161</v>
+        <v>9.505736753899704</v>
       </c>
       <c r="I31" t="n">
-        <v>16.16782834495012</v>
+        <v>16.63503931932448</v>
       </c>
       <c r="J31" t="n">
-        <v>79.59546262129288</v>
+        <v>84.36341369085987</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -1823,7 +1823,7 @@
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>4</v>
+        <v>3.974986522911051</v>
       </c>
     </row>
     <row r="32">
@@ -1831,7 +1831,7 @@
         <v>41847</v>
       </c>
       <c r="B32" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C32" t="n">
         <v>5</v>
@@ -1846,16 +1846,16 @@
         <v>2</v>
       </c>
       <c r="G32" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H32" t="n">
-        <v>8.705753724203909</v>
+        <v>9.505736753899704</v>
       </c>
       <c r="I32" t="n">
-        <v>16.16782834495012</v>
+        <v>15.44682222508702</v>
       </c>
       <c r="J32" t="n">
-        <v>82.08282082820828</v>
+        <v>86.7398478793348</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -1867,7 +1867,7 @@
         <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>4</v>
+        <v>3.974986522911051</v>
       </c>
     </row>
     <row r="33">
@@ -1890,16 +1890,16 @@
         <v>2</v>
       </c>
       <c r="G33" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H33" t="n">
-        <v>8.705753724203909</v>
+        <v>9.505736753899704</v>
       </c>
       <c r="I33" t="n">
-        <v>14.92414924149242</v>
+        <v>15.44682222508702</v>
       </c>
       <c r="J33" t="n">
-        <v>79.59546262129288</v>
+        <v>80.79876240814748</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -1911,7 +1911,7 @@
         <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>4</v>
+        <v>3.974986522911051</v>
       </c>
     </row>
     <row r="34">
@@ -1919,7 +1919,7 @@
         <v>41861</v>
       </c>
       <c r="B34" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C34" t="n">
         <v>4</v>
@@ -1934,16 +1934,16 @@
         <v>2</v>
       </c>
       <c r="G34" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H34" t="n">
-        <v>9.94943282766161</v>
+        <v>9.505736753899704</v>
       </c>
       <c r="I34" t="n">
-        <v>16.16782834495012</v>
+        <v>17.82325641356195</v>
       </c>
       <c r="J34" t="n">
-        <v>77.10810441437748</v>
+        <v>81.98697950238495</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>3</v>
+        <v>2.981239892183289</v>
       </c>
     </row>
     <row r="35">
@@ -1963,7 +1963,7 @@
         <v>41868</v>
       </c>
       <c r="B35" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C35" t="n">
         <v>4</v>
@@ -1978,16 +1978,16 @@
         <v>2</v>
       </c>
       <c r="G35" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H35" t="n">
-        <v>11.19311193111931</v>
+        <v>8.317519659662242</v>
       </c>
       <c r="I35" t="n">
-        <v>16.16782834495012</v>
+        <v>16.63503931932448</v>
       </c>
       <c r="J35" t="n">
-        <v>79.59546262129288</v>
+        <v>80.79876240814748</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -1999,7 +1999,7 @@
         <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>4</v>
+        <v>3.974986522911051</v>
       </c>
     </row>
     <row r="36">
@@ -2007,7 +2007,7 @@
         <v>41875</v>
       </c>
       <c r="B36" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C36" t="n">
         <v>5</v>
@@ -2022,16 +2022,16 @@
         <v>2</v>
       </c>
       <c r="G36" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H36" t="n">
-        <v>8.705753724203909</v>
+        <v>8.317519659662242</v>
       </c>
       <c r="I36" t="n">
-        <v>14.92414924149242</v>
+        <v>16.63503931932448</v>
       </c>
       <c r="J36" t="n">
-        <v>79.59546262129288</v>
+        <v>78.42232821967256</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -2043,7 +2043,7 @@
         <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>4</v>
+        <v>3.974986522911051</v>
       </c>
     </row>
     <row r="37">
@@ -2051,7 +2051,7 @@
         <v>41882</v>
       </c>
       <c r="B37" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C37" t="n">
         <v>4</v>
@@ -2066,16 +2066,16 @@
         <v>2</v>
       </c>
       <c r="G37" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H37" t="n">
-        <v>8.705753724203909</v>
+        <v>9.505736753899704</v>
       </c>
       <c r="I37" t="n">
-        <v>17.41150744840782</v>
+        <v>17.82325641356195</v>
       </c>
       <c r="J37" t="n">
-        <v>82.08282082820828</v>
+        <v>83.17519659662241</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
@@ -2087,7 +2087,7 @@
         <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>3</v>
+        <v>2.981239892183289</v>
       </c>
     </row>
     <row r="38">
@@ -2095,7 +2095,7 @@
         <v>41889</v>
       </c>
       <c r="B38" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C38" t="n">
         <v>4</v>
@@ -2110,16 +2110,16 @@
         <v>2</v>
       </c>
       <c r="G38" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H38" t="n">
-        <v>9.94943282766161</v>
+        <v>9.505736753899704</v>
       </c>
       <c r="I38" t="n">
-        <v>17.41150744840782</v>
+        <v>17.82325641356195</v>
       </c>
       <c r="J38" t="n">
-        <v>85.81385813858139</v>
+        <v>85.55163078509733</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -2131,7 +2131,7 @@
         <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>3</v>
+        <v>2.981239892183289</v>
       </c>
     </row>
     <row r="39">
@@ -2154,16 +2154,16 @@
         <v>2</v>
       </c>
       <c r="G39" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H39" t="n">
-        <v>9.94943282766161</v>
+        <v>9.505736753899704</v>
       </c>
       <c r="I39" t="n">
-        <v>16.16782834495012</v>
+        <v>16.63503931932448</v>
       </c>
       <c r="J39" t="n">
-        <v>83.32649993166598</v>
+        <v>84.36341369085987</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -2175,7 +2175,7 @@
         <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>4</v>
+        <v>3.974986522911051</v>
       </c>
     </row>
     <row r="40">
@@ -2183,7 +2183,7 @@
         <v>41903</v>
       </c>
       <c r="B40" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C40" t="n">
         <v>4</v>
@@ -2198,16 +2198,16 @@
         <v>2</v>
       </c>
       <c r="G40" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H40" t="n">
-        <v>9.94943282766161</v>
+        <v>9.505736753899704</v>
       </c>
       <c r="I40" t="n">
-        <v>14.92414924149242</v>
+        <v>15.44682222508702</v>
       </c>
       <c r="J40" t="n">
-        <v>80.83914172475059</v>
+        <v>80.79876240814748</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -2219,7 +2219,7 @@
         <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>3</v>
+        <v>2.981239892183289</v>
       </c>
     </row>
     <row r="41">
@@ -2242,16 +2242,16 @@
         <v>2</v>
       </c>
       <c r="G41" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H41" t="n">
-        <v>9.94943282766161</v>
+        <v>9.505736753899704</v>
       </c>
       <c r="I41" t="n">
-        <v>14.92414924149242</v>
+        <v>14.25860513084956</v>
       </c>
       <c r="J41" t="n">
-        <v>82.08282082820828</v>
+        <v>80.79876240814748</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -2263,7 +2263,7 @@
         <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>3</v>
+        <v>2.981239892183289</v>
       </c>
     </row>
     <row r="42">
@@ -2271,7 +2271,7 @@
         <v>41917</v>
       </c>
       <c r="B42" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C42" t="n">
         <v>4</v>
@@ -2280,22 +2280,22 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F42" t="n">
         <v>2</v>
       </c>
       <c r="G42" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H42" t="n">
-        <v>8.705753724203909</v>
+        <v>9.505736753899704</v>
       </c>
       <c r="I42" t="n">
-        <v>16.16782834495012</v>
+        <v>16.63503931932448</v>
       </c>
       <c r="J42" t="n">
-        <v>84.57017903512369</v>
+        <v>84.36341369085987</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -2307,7 +2307,7 @@
         <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>3</v>
+        <v>2.981239892183289</v>
       </c>
     </row>
     <row r="43">
@@ -2315,7 +2315,7 @@
         <v>41924</v>
       </c>
       <c r="B43" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C43" t="n">
         <v>4</v>
@@ -2330,16 +2330,16 @@
         <v>2</v>
       </c>
       <c r="G43" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H43" t="n">
-        <v>8.705753724203909</v>
+        <v>8.317519659662242</v>
       </c>
       <c r="I43" t="n">
-        <v>14.92414924149242</v>
+        <v>15.44682222508702</v>
       </c>
       <c r="J43" t="n">
-        <v>83.32649993166598</v>
+        <v>85.55163078509733</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -2351,7 +2351,7 @@
         <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>3</v>
+        <v>2.981239892183289</v>
       </c>
     </row>
     <row r="44">
@@ -2359,7 +2359,7 @@
         <v>41931</v>
       </c>
       <c r="B44" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C44" t="n">
         <v>4</v>
@@ -2374,16 +2374,16 @@
         <v>2</v>
       </c>
       <c r="G44" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H44" t="n">
-        <v>8.705753724203909</v>
+        <v>9.505736753899704</v>
       </c>
       <c r="I44" t="n">
-        <v>16.16782834495012</v>
+        <v>16.63503931932448</v>
       </c>
       <c r="J44" t="n">
-        <v>82.08282082820828</v>
+        <v>83.17519659662241</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
@@ -2395,7 +2395,7 @@
         <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>4</v>
+        <v>3.974986522911051</v>
       </c>
     </row>
     <row r="45">
@@ -2403,7 +2403,7 @@
         <v>41938</v>
       </c>
       <c r="B45" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C45" t="n">
         <v>4</v>
@@ -2418,16 +2418,16 @@
         <v>2</v>
       </c>
       <c r="G45" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H45" t="n">
-        <v>8.705753724203909</v>
+        <v>9.505736753899704</v>
       </c>
       <c r="I45" t="n">
-        <v>17.41150744840782</v>
+        <v>16.63503931932448</v>
       </c>
       <c r="J45" t="n">
-        <v>82.08282082820828</v>
+        <v>84.36341369085987</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
@@ -2439,7 +2439,7 @@
         <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>4</v>
+        <v>2.981239892183289</v>
       </c>
     </row>
     <row r="46">
@@ -2456,22 +2456,22 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F46" t="n">
         <v>2</v>
       </c>
       <c r="G46" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H46" t="n">
-        <v>12.43679103457701</v>
+        <v>10.69395384813717</v>
       </c>
       <c r="I46" t="n">
-        <v>16.16782834495012</v>
+        <v>16.63503931932448</v>
       </c>
       <c r="J46" t="n">
-        <v>83.32649993166598</v>
+        <v>73.6694598427227</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
@@ -2483,7 +2483,7 @@
         <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>4</v>
+        <v>3.974986522911051</v>
       </c>
     </row>
     <row r="47">
@@ -2491,7 +2491,7 @@
         <v>41952</v>
       </c>
       <c r="B47" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C47" t="n">
         <v>4</v>
@@ -2506,16 +2506,16 @@
         <v>2</v>
       </c>
       <c r="G47" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H47" t="n">
-        <v>9.94943282766161</v>
+        <v>9.505736753899704</v>
       </c>
       <c r="I47" t="n">
-        <v>14.92414924149242</v>
+        <v>14.25860513084956</v>
       </c>
       <c r="J47" t="n">
-        <v>84.57017903512369</v>
+        <v>86.7398478793348</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
         <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>3</v>
+        <v>2.981239892183289</v>
       </c>
     </row>
     <row r="48">
@@ -2535,7 +2535,7 @@
         <v>41959</v>
       </c>
       <c r="B48" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C48" t="n">
         <v>4</v>
@@ -2550,16 +2550,16 @@
         <v>2</v>
       </c>
       <c r="G48" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H48" t="n">
-        <v>9.94943282766161</v>
+        <v>9.505736753899704</v>
       </c>
       <c r="I48" t="n">
-        <v>17.41150744840782</v>
+        <v>15.44682222508702</v>
       </c>
       <c r="J48" t="n">
-        <v>88.30121634549678</v>
+        <v>83.17519659662241</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
@@ -2571,7 +2571,7 @@
         <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>3</v>
+        <v>2.981239892183289</v>
       </c>
     </row>
     <row r="49">
@@ -2579,7 +2579,7 @@
         <v>41966</v>
       </c>
       <c r="B49" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C49" t="n">
         <v>4</v>
@@ -2594,16 +2594,16 @@
         <v>2</v>
       </c>
       <c r="G49" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H49" t="n">
-        <v>8.705753724203909</v>
+        <v>9.505736753899704</v>
       </c>
       <c r="I49" t="n">
-        <v>14.92414924149242</v>
+        <v>14.25860513084956</v>
       </c>
       <c r="J49" t="n">
-        <v>77.10810441437748</v>
+        <v>77.23411112543509</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
@@ -2615,7 +2615,7 @@
         <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>3</v>
+        <v>2.981239892183289</v>
       </c>
     </row>
     <row r="50">
@@ -2623,7 +2623,7 @@
         <v>41973</v>
       </c>
       <c r="B50" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C50" t="n">
         <v>4</v>
@@ -2638,16 +2638,16 @@
         <v>2</v>
       </c>
       <c r="G50" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H50" t="n">
-        <v>9.94943282766161</v>
+        <v>9.505736753899704</v>
       </c>
       <c r="I50" t="n">
-        <v>14.92414924149242</v>
+        <v>14.25860513084956</v>
       </c>
       <c r="J50" t="n">
-        <v>82.08282082820828</v>
+        <v>81.98697950238495</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
@@ -2659,7 +2659,7 @@
         <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>4</v>
+        <v>3.974986522911051</v>
       </c>
     </row>
     <row r="51">
@@ -2682,16 +2682,16 @@
         <v>2</v>
       </c>
       <c r="G51" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H51" t="n">
-        <v>8.705753724203909</v>
+        <v>9.505736753899704</v>
       </c>
       <c r="I51" t="n">
-        <v>17.41150744840782</v>
+        <v>17.82325641356195</v>
       </c>
       <c r="J51" t="n">
-        <v>78.35178351783517</v>
+        <v>78.42232821967256</v>
       </c>
       <c r="K51" t="n">
         <v>0</v>
@@ -2703,7 +2703,7 @@
         <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>3</v>
+        <v>2.981239892183289</v>
       </c>
     </row>
     <row r="52">
@@ -2711,7 +2711,7 @@
         <v>41987</v>
       </c>
       <c r="B52" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C52" t="n">
         <v>4</v>
@@ -2726,16 +2726,16 @@
         <v>2</v>
       </c>
       <c r="G52" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H52" t="n">
-        <v>8.705753724203909</v>
+        <v>8.317519659662242</v>
       </c>
       <c r="I52" t="n">
-        <v>14.92414924149242</v>
+        <v>15.44682222508702</v>
       </c>
       <c r="J52" t="n">
-        <v>74.62074620746208</v>
+        <v>76.04589403119763</v>
       </c>
       <c r="K52" t="n">
         <v>0</v>
@@ -2747,7 +2747,7 @@
         <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>3</v>
+        <v>2.981239892183289</v>
       </c>
     </row>
     <row r="53">
@@ -2764,22 +2764,22 @@
         <v>3</v>
       </c>
       <c r="E53" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F53" t="n">
         <v>2</v>
       </c>
       <c r="G53" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H53" t="n">
-        <v>8.705753724203909</v>
+        <v>9.505736753899704</v>
       </c>
       <c r="I53" t="n">
-        <v>22.38622386223862</v>
+        <v>22.5761247905118</v>
       </c>
       <c r="J53" t="n">
-        <v>70.88970889708898</v>
+        <v>70.10480856001031</v>
       </c>
       <c r="K53" t="n">
         <v>0</v>
@@ -2791,7 +2791,7 @@
         <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>3</v>
+        <v>2.981239892183289</v>
       </c>
     </row>
     <row r="54">
@@ -2802,7 +2802,7 @@
         <v>62</v>
       </c>
       <c r="C54" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D54" t="n">
         <v>2</v>
@@ -2814,16 +2814,16 @@
         <v>2</v>
       </c>
       <c r="G54" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H54" t="n">
-        <v>8.705753724203909</v>
+        <v>8.317519659662242</v>
       </c>
       <c r="I54" t="n">
-        <v>21.14254475878092</v>
+        <v>21.38790769627433</v>
       </c>
       <c r="J54" t="n">
-        <v>77.10810441437748</v>
+        <v>77.23411112543509</v>
       </c>
       <c r="K54" t="n">
         <v>0</v>
@@ -2835,7 +2835,7 @@
         <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>3</v>
+        <v>2.981239892183289</v>
       </c>
     </row>
     <row r="55">
@@ -2843,7 +2843,7 @@
         <v>42008</v>
       </c>
       <c r="B55" t="n">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="C55" t="n">
         <v>4</v>
@@ -2858,16 +2858,16 @@
         <v>2</v>
       </c>
       <c r="G55" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H55" t="n">
-        <v>8.705753724203909</v>
+        <v>9.505736753899704</v>
       </c>
       <c r="I55" t="n">
-        <v>18.65518655186552</v>
+        <v>19.01147350779941</v>
       </c>
       <c r="J55" t="n">
-        <v>83.32649993166598</v>
+        <v>83.17519659662241</v>
       </c>
       <c r="K55" t="n">
         <v>0</v>
@@ -2879,7 +2879,7 @@
         <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>3</v>
+        <v>2.981239892183289</v>
       </c>
     </row>
     <row r="56">
@@ -2887,13 +2887,13 @@
         <v>42015</v>
       </c>
       <c r="B56" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C56" t="n">
         <v>4</v>
       </c>
       <c r="D56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E56" t="n">
         <v>6</v>
@@ -2902,16 +2902,16 @@
         <v>2</v>
       </c>
       <c r="G56" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H56" t="n">
-        <v>8.705753724203909</v>
+        <v>8.317519659662242</v>
       </c>
       <c r="I56" t="n">
-        <v>16.16782834495012</v>
+        <v>15.44682222508702</v>
       </c>
       <c r="J56" t="n">
-        <v>80.83914172475059</v>
+        <v>84.36341369085987</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -2923,7 +2923,7 @@
         <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>3</v>
+        <v>2.981239892183289</v>
       </c>
     </row>
     <row r="57">
@@ -2946,16 +2946,16 @@
         <v>2</v>
       </c>
       <c r="G57" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H57" t="n">
-        <v>8.705753724203909</v>
+        <v>8.317519659662242</v>
       </c>
       <c r="I57" t="n">
-        <v>17.41150744840782</v>
+        <v>17.82325641356195</v>
       </c>
       <c r="J57" t="n">
-        <v>80.83914172475059</v>
+        <v>80.79876240814748</v>
       </c>
       <c r="K57" t="n">
         <v>0</v>
@@ -2967,7 +2967,7 @@
         <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>3</v>
+        <v>2.981239892183289</v>
       </c>
     </row>
     <row r="58">
@@ -2975,7 +2975,7 @@
         <v>42029</v>
       </c>
       <c r="B58" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C58" t="n">
         <v>4</v>
@@ -2990,16 +2990,16 @@
         <v>2</v>
       </c>
       <c r="G58" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H58" t="n">
-        <v>9.94943282766161</v>
+        <v>9.505736753899704</v>
       </c>
       <c r="I58" t="n">
-        <v>17.41150744840782</v>
+        <v>17.82325641356195</v>
       </c>
       <c r="J58" t="n">
-        <v>73.37706710400437</v>
+        <v>78.42232821967256</v>
       </c>
       <c r="K58" t="n">
         <v>0</v>
@@ -3011,7 +3011,7 @@
         <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>3</v>
+        <v>2.981239892183289</v>
       </c>
     </row>
     <row r="59">
@@ -3019,7 +3019,7 @@
         <v>42036</v>
       </c>
       <c r="B59" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C59" t="n">
         <v>4</v>
@@ -3028,22 +3028,22 @@
         <v>2</v>
       </c>
       <c r="E59" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F59" t="n">
         <v>2</v>
       </c>
       <c r="G59" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H59" t="n">
-        <v>9.94943282766161</v>
+        <v>9.505736753899704</v>
       </c>
       <c r="I59" t="n">
-        <v>17.41150744840782</v>
+        <v>17.82325641356195</v>
       </c>
       <c r="J59" t="n">
-        <v>74.62074620746208</v>
+        <v>76.04589403119763</v>
       </c>
       <c r="K59" t="n">
         <v>0</v>
@@ -3055,7 +3055,7 @@
         <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>3</v>
+        <v>2.981239892183289</v>
       </c>
     </row>
     <row r="60">
@@ -3078,16 +3078,16 @@
         <v>2</v>
       </c>
       <c r="G60" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H60" t="n">
-        <v>8.705753724203909</v>
+        <v>9.505736753899704</v>
       </c>
       <c r="I60" t="n">
-        <v>17.41150744840782</v>
+        <v>17.82325641356195</v>
       </c>
       <c r="J60" t="n">
-        <v>73.37706710400437</v>
+        <v>72.48124274848524</v>
       </c>
       <c r="K60" t="n">
         <v>0</v>
@@ -3099,7 +3099,7 @@
         <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>3</v>
+        <v>2.981239892183289</v>
       </c>
     </row>
     <row r="61">
@@ -3107,7 +3107,7 @@
         <v>42050</v>
       </c>
       <c r="B61" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C61" t="n">
         <v>4</v>
@@ -3122,16 +3122,16 @@
         <v>2</v>
       </c>
       <c r="G61" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H61" t="n">
-        <v>8.705753724203909</v>
+        <v>9.505736753899704</v>
       </c>
       <c r="I61" t="n">
-        <v>17.41150744840782</v>
+        <v>17.82325641356195</v>
       </c>
       <c r="J61" t="n">
-        <v>75.86442531091978</v>
+        <v>78.42232821967256</v>
       </c>
       <c r="K61" t="n">
         <v>0</v>
@@ -3143,7 +3143,7 @@
         <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>3</v>
+        <v>2.981239892183289</v>
       </c>
     </row>
     <row r="62">
@@ -3151,7 +3151,7 @@
         <v>42057</v>
       </c>
       <c r="B62" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C62" t="n">
         <v>4</v>
@@ -3166,16 +3166,16 @@
         <v>2</v>
       </c>
       <c r="G62" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H62" t="n">
-        <v>9.94943282766161</v>
+        <v>9.505736753899704</v>
       </c>
       <c r="I62" t="n">
-        <v>17.41150744840782</v>
+        <v>16.63503931932448</v>
       </c>
       <c r="J62" t="n">
-        <v>78.35178351783517</v>
+        <v>78.42232821967256</v>
       </c>
       <c r="K62" t="n">
         <v>0</v>
@@ -3187,7 +3187,7 @@
         <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>3</v>
+        <v>2.981239892183289</v>
       </c>
     </row>
     <row r="63">
@@ -3210,16 +3210,16 @@
         <v>2</v>
       </c>
       <c r="G63" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H63" t="n">
-        <v>8.705753724203909</v>
+        <v>8.317519659662242</v>
       </c>
       <c r="I63" t="n">
-        <v>14.92414924149242</v>
+        <v>16.63503931932448</v>
       </c>
       <c r="J63" t="n">
-        <v>80.83914172475059</v>
+        <v>79.61054531391002</v>
       </c>
       <c r="K63" t="n">
         <v>0</v>
@@ -3231,7 +3231,7 @@
         <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>3</v>
+        <v>2.981239892183289</v>
       </c>
     </row>
     <row r="64">
@@ -3239,7 +3239,7 @@
         <v>42071</v>
       </c>
       <c r="B64" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C64" t="n">
         <v>4</v>
@@ -3254,16 +3254,16 @@
         <v>2</v>
       </c>
       <c r="G64" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H64" t="n">
-        <v>8.705753724203909</v>
+        <v>9.505736753899704</v>
       </c>
       <c r="I64" t="n">
-        <v>16.16782834495012</v>
+        <v>16.63503931932448</v>
       </c>
       <c r="J64" t="n">
-        <v>79.59546262129288</v>
+        <v>79.61054531391002</v>
       </c>
       <c r="K64" t="n">
         <v>0</v>
@@ -3275,7 +3275,7 @@
         <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>3</v>
+        <v>2.981239892183289</v>
       </c>
     </row>
     <row r="65">
@@ -3283,7 +3283,7 @@
         <v>42078</v>
       </c>
       <c r="B65" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C65" t="n">
         <v>4</v>
@@ -3298,16 +3298,16 @@
         <v>2</v>
       </c>
       <c r="G65" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H65" t="n">
-        <v>8.705753724203909</v>
+        <v>8.317519659662242</v>
       </c>
       <c r="I65" t="n">
-        <v>17.41150744840782</v>
+        <v>17.82325641356195</v>
       </c>
       <c r="J65" t="n">
-        <v>87.05753724203909</v>
+        <v>85.55163078509733</v>
       </c>
       <c r="K65" t="n">
         <v>0</v>
@@ -3319,7 +3319,7 @@
         <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>3</v>
+        <v>2.981239892183289</v>
       </c>
     </row>
     <row r="66">
@@ -3327,7 +3327,7 @@
         <v>42085</v>
       </c>
       <c r="B66" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C66" t="n">
         <v>5</v>
@@ -3342,16 +3342,16 @@
         <v>2</v>
       </c>
       <c r="G66" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H66" t="n">
-        <v>11.19311193111931</v>
+        <v>10.69395384813717</v>
       </c>
       <c r="I66" t="n">
-        <v>17.41150744840782</v>
+        <v>17.82325641356195</v>
       </c>
       <c r="J66" t="n">
-        <v>79.59546262129288</v>
+        <v>83.17519659662241</v>
       </c>
       <c r="K66" t="n">
         <v>0</v>
@@ -3363,7 +3363,7 @@
         <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>3</v>
+        <v>3.974986522911051</v>
       </c>
     </row>
     <row r="67">
@@ -3380,22 +3380,22 @@
         <v>2</v>
       </c>
       <c r="E67" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F67" t="n">
         <v>2</v>
       </c>
       <c r="G67" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H67" t="n">
-        <v>8.705753724203909</v>
+        <v>9.505736753899704</v>
       </c>
       <c r="I67" t="n">
-        <v>19.89886565532322</v>
+        <v>20.19969060203687</v>
       </c>
       <c r="J67" t="n">
-        <v>83.32649993166598</v>
+        <v>87.92806497357226</v>
       </c>
       <c r="K67" t="n">
         <v>0</v>
@@ -3407,7 +3407,7 @@
         <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>3</v>
+        <v>2.981239892183289</v>
       </c>
     </row>
     <row r="68">
@@ -3430,16 +3430,16 @@
         <v>2</v>
       </c>
       <c r="G68" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H68" t="n">
-        <v>8.705753724203909</v>
+        <v>8.317519659662242</v>
       </c>
       <c r="I68" t="n">
-        <v>17.41150744840782</v>
+        <v>17.82325641356195</v>
       </c>
       <c r="J68" t="n">
-        <v>74.62074620746208</v>
+        <v>77.23411112543509</v>
       </c>
       <c r="K68" t="n">
         <v>0</v>
@@ -3451,7 +3451,7 @@
         <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>3</v>
+        <v>2.981239892183289</v>
       </c>
     </row>
     <row r="69">
@@ -3459,7 +3459,7 @@
         <v>42106</v>
       </c>
       <c r="B69" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C69" t="n">
         <v>4</v>
@@ -3474,16 +3474,16 @@
         <v>2</v>
       </c>
       <c r="G69" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H69" t="n">
-        <v>8.705753724203909</v>
+        <v>8.317519659662242</v>
       </c>
       <c r="I69" t="n">
-        <v>14.92414924149242</v>
+        <v>14.25860513084956</v>
       </c>
       <c r="J69" t="n">
-        <v>77.10810441437748</v>
+        <v>74.85767693696017</v>
       </c>
       <c r="K69" t="n">
         <v>0</v>
@@ -3495,7 +3495,7 @@
         <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>3</v>
+        <v>2.981239892183289</v>
       </c>
     </row>
     <row r="70">
@@ -3503,7 +3503,7 @@
         <v>42113</v>
       </c>
       <c r="B70" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C70" t="n">
         <v>4</v>
@@ -3518,16 +3518,16 @@
         <v>2</v>
       </c>
       <c r="G70" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H70" t="n">
-        <v>8.705753724203909</v>
+        <v>9.505736753899704</v>
       </c>
       <c r="I70" t="n">
-        <v>16.16782834495012</v>
+        <v>16.63503931932448</v>
       </c>
       <c r="J70" t="n">
-        <v>77.10810441437748</v>
+        <v>77.23411112543509</v>
       </c>
       <c r="K70" t="n">
         <v>0</v>
@@ -3539,7 +3539,7 @@
         <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>3</v>
+        <v>2.981239892183289</v>
       </c>
     </row>
     <row r="71">
@@ -3562,16 +3562,16 @@
         <v>2</v>
       </c>
       <c r="G71" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H71" t="n">
-        <v>8.705753724203909</v>
+        <v>9.505736753899704</v>
       </c>
       <c r="I71" t="n">
-        <v>19.89886565532322</v>
+        <v>21.38790769627433</v>
       </c>
       <c r="J71" t="n">
-        <v>83.32649993166598</v>
+        <v>79.61054531391002</v>
       </c>
       <c r="K71" t="n">
         <v>0</v>
@@ -3583,7 +3583,7 @@
         <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>3</v>
+        <v>2.981239892183289</v>
       </c>
     </row>
     <row r="72">
@@ -3591,7 +3591,7 @@
         <v>42127</v>
       </c>
       <c r="B72" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C72" t="n">
         <v>4</v>
@@ -3606,16 +3606,16 @@
         <v>2</v>
       </c>
       <c r="G72" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H72" t="n">
-        <v>8.705753724203909</v>
+        <v>8.317519659662242</v>
       </c>
       <c r="I72" t="n">
-        <v>17.41150744840782</v>
+        <v>17.82325641356195</v>
       </c>
       <c r="J72" t="n">
-        <v>77.10810441437748</v>
+        <v>79.61054531391002</v>
       </c>
       <c r="K72" t="n">
         <v>0</v>
@@ -3627,7 +3627,7 @@
         <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>3</v>
+        <v>2.981239892183289</v>
       </c>
     </row>
     <row r="73">
@@ -3650,16 +3650,16 @@
         <v>2</v>
       </c>
       <c r="G73" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H73" t="n">
-        <v>8.705753724203909</v>
+        <v>8.317519659662242</v>
       </c>
       <c r="I73" t="n">
-        <v>18.65518655186552</v>
+        <v>19.01147350779941</v>
       </c>
       <c r="J73" t="n">
-        <v>77.10810441437748</v>
+        <v>78.42232821967256</v>
       </c>
       <c r="K73" t="n">
         <v>0</v>
@@ -3671,7 +3671,7 @@
         <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>3</v>
+        <v>2.981239892183289</v>
       </c>
     </row>
     <row r="74">
@@ -3679,7 +3679,7 @@
         <v>42141</v>
       </c>
       <c r="B74" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C74" t="n">
         <v>4</v>
@@ -3694,16 +3694,16 @@
         <v>2</v>
       </c>
       <c r="G74" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H74" t="n">
-        <v>8.705753724203909</v>
+        <v>9.505736753899704</v>
       </c>
       <c r="I74" t="n">
-        <v>16.16782834495012</v>
+        <v>16.63503931932448</v>
       </c>
       <c r="J74" t="n">
-        <v>82.08282082820828</v>
+        <v>83.17519659662241</v>
       </c>
       <c r="K74" t="n">
         <v>0</v>
@@ -3715,7 +3715,7 @@
         <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>3</v>
+        <v>2.981239892183289</v>
       </c>
     </row>
     <row r="75">
@@ -3738,16 +3738,16 @@
         <v>2</v>
       </c>
       <c r="G75" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H75" t="n">
-        <v>8.705753724203909</v>
+        <v>9.505736753899704</v>
       </c>
       <c r="I75" t="n">
-        <v>17.41150744840782</v>
+        <v>17.82325641356195</v>
       </c>
       <c r="J75" t="n">
-        <v>75.86442531091978</v>
+        <v>79.61054531391002</v>
       </c>
       <c r="K75" t="n">
         <v>0</v>
@@ -3759,7 +3759,7 @@
         <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>3</v>
+        <v>2.981239892183289</v>
       </c>
     </row>
     <row r="76">
@@ -3767,7 +3767,7 @@
         <v>42155</v>
       </c>
       <c r="B76" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C76" t="n">
         <v>4</v>
@@ -3782,16 +3782,16 @@
         <v>2</v>
       </c>
       <c r="G76" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H76" t="n">
-        <v>11.19311193111931</v>
+        <v>10.69395384813717</v>
       </c>
       <c r="I76" t="n">
-        <v>18.65518655186552</v>
+        <v>17.82325641356195</v>
       </c>
       <c r="J76" t="n">
-        <v>79.59546262129288</v>
+        <v>84.36341369085987</v>
       </c>
       <c r="K76" t="n">
         <v>0</v>
@@ -3803,7 +3803,7 @@
         <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>3</v>
+        <v>2.981239892183289</v>
       </c>
     </row>
     <row r="77">
@@ -3826,16 +3826,16 @@
         <v>2</v>
       </c>
       <c r="G77" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H77" t="n">
-        <v>9.94943282766161</v>
+        <v>10.69395384813717</v>
       </c>
       <c r="I77" t="n">
-        <v>18.65518655186552</v>
+        <v>19.01147350779941</v>
       </c>
       <c r="J77" t="n">
-        <v>79.59546262129288</v>
+        <v>84.36341369085987</v>
       </c>
       <c r="K77" t="n">
         <v>0</v>
@@ -3847,7 +3847,7 @@
         <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>3</v>
+        <v>2.981239892183289</v>
       </c>
     </row>
     <row r="78">
@@ -3855,7 +3855,7 @@
         <v>42169</v>
       </c>
       <c r="B78" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C78" t="n">
         <v>4</v>
@@ -3870,16 +3870,16 @@
         <v>2</v>
       </c>
       <c r="G78" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H78" t="n">
-        <v>12.43679103457701</v>
+        <v>13.07038803661209</v>
       </c>
       <c r="I78" t="n">
-        <v>19.89886565532322</v>
+        <v>19.01147350779941</v>
       </c>
       <c r="J78" t="n">
-        <v>85.81385813858139</v>
+        <v>84.36341369085987</v>
       </c>
       <c r="K78" t="n">
         <v>0</v>
@@ -3891,7 +3891,7 @@
         <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>3</v>
+        <v>2.981239892183289</v>
       </c>
     </row>
     <row r="79">
@@ -3914,16 +3914,16 @@
         <v>2</v>
       </c>
       <c r="G79" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H79" t="n">
-        <v>12.43679103457701</v>
+        <v>13.07038803661209</v>
       </c>
       <c r="I79" t="n">
-        <v>17.41150744840782</v>
+        <v>17.82325641356195</v>
       </c>
       <c r="J79" t="n">
-        <v>78.35178351783517</v>
+        <v>79.61054531391002</v>
       </c>
       <c r="K79" t="n">
         <v>0</v>
@@ -3935,7 +3935,7 @@
         <v>0</v>
       </c>
       <c r="N79" t="n">
-        <v>3</v>
+        <v>2.981239892183289</v>
       </c>
     </row>
     <row r="80">
@@ -3943,7 +3943,7 @@
         <v>42183</v>
       </c>
       <c r="B80" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C80" t="n">
         <v>4</v>
@@ -3958,16 +3958,16 @@
         <v>2</v>
       </c>
       <c r="G80" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H80" t="n">
-        <v>9.94943282766161</v>
+        <v>10.69395384813717</v>
       </c>
       <c r="I80" t="n">
-        <v>16.16782834495012</v>
+        <v>16.63503931932448</v>
       </c>
       <c r="J80" t="n">
-        <v>78.35178351783517</v>
+        <v>77.23411112543509</v>
       </c>
       <c r="K80" t="n">
         <v>0</v>
@@ -3979,7 +3979,7 @@
         <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>3</v>
+        <v>2.981239892183289</v>
       </c>
     </row>
     <row r="81">
@@ -3987,7 +3987,7 @@
         <v>42190</v>
       </c>
       <c r="B81" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C81" t="n">
         <v>5</v>
@@ -4002,16 +4002,16 @@
         <v>2</v>
       </c>
       <c r="G81" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H81" t="n">
-        <v>11.19311193111931</v>
+        <v>11.88217094237463</v>
       </c>
       <c r="I81" t="n">
-        <v>18.65518655186552</v>
+        <v>20.19969060203687</v>
       </c>
       <c r="J81" t="n">
-        <v>80.83914172475059</v>
+        <v>78.42232821967256</v>
       </c>
       <c r="K81" t="n">
         <v>0</v>
@@ -4023,7 +4023,7 @@
         <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>3</v>
+        <v>2.981239892183289</v>
       </c>
     </row>
     <row r="82">
@@ -4046,16 +4046,16 @@
         <v>2</v>
       </c>
       <c r="G82" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H82" t="n">
-        <v>9.94943282766161</v>
+        <v>10.69395384813717</v>
       </c>
       <c r="I82" t="n">
-        <v>17.41150744840782</v>
+        <v>17.82325641356195</v>
       </c>
       <c r="J82" t="n">
-        <v>74.62074620746208</v>
+        <v>78.42232821967256</v>
       </c>
       <c r="K82" t="n">
         <v>0</v>
@@ -4067,7 +4067,7 @@
         <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>3</v>
+        <v>2.981239892183289</v>
       </c>
     </row>
     <row r="83">
@@ -4075,13 +4075,13 @@
         <v>42204</v>
       </c>
       <c r="B83" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C83" t="n">
         <v>4</v>
       </c>
       <c r="D83" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E83" t="n">
         <v>6</v>
@@ -4090,16 +4090,16 @@
         <v>2</v>
       </c>
       <c r="G83" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H83" t="n">
-        <v>9.94943282766161</v>
+        <v>10.69395384813717</v>
       </c>
       <c r="I83" t="n">
-        <v>19.89886565532322</v>
+        <v>20.19969060203687</v>
       </c>
       <c r="J83" t="n">
-        <v>78.35178351783517</v>
+        <v>79.61054531391002</v>
       </c>
       <c r="K83" t="n">
         <v>0</v>
@@ -4111,7 +4111,7 @@
         <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>3</v>
+        <v>2.981239892183289</v>
       </c>
     </row>
     <row r="84">
@@ -4134,16 +4134,16 @@
         <v>2</v>
       </c>
       <c r="G84" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H84" t="n">
-        <v>11.19311193111931</v>
+        <v>10.69395384813717</v>
       </c>
       <c r="I84" t="n">
-        <v>18.65518655186552</v>
+        <v>19.01147350779941</v>
       </c>
       <c r="J84" t="n">
-        <v>78.35178351783517</v>
+        <v>76.04589403119763</v>
       </c>
       <c r="K84" t="n">
         <v>0</v>
@@ -4155,7 +4155,7 @@
         <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>3</v>
+        <v>2.981239892183289</v>
       </c>
     </row>
     <row r="85">
@@ -4163,7 +4163,7 @@
         <v>42218</v>
       </c>
       <c r="B85" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C85" t="n">
         <v>4</v>
@@ -4178,16 +4178,16 @@
         <v>2</v>
       </c>
       <c r="G85" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H85" t="n">
-        <v>11.19311193111931</v>
+        <v>10.69395384813717</v>
       </c>
       <c r="I85" t="n">
-        <v>18.65518655186552</v>
+        <v>17.82325641356195</v>
       </c>
       <c r="J85" t="n">
-        <v>72.13338800054667</v>
+        <v>79.61054531391002</v>
       </c>
       <c r="K85" t="n">
         <v>0</v>
@@ -4199,7 +4199,7 @@
         <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>3</v>
+        <v>2.981239892183289</v>
       </c>
     </row>
     <row r="86">
@@ -4222,16 +4222,16 @@
         <v>2</v>
       </c>
       <c r="G86" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H86" t="n">
-        <v>11.19311193111931</v>
+        <v>10.69395384813717</v>
       </c>
       <c r="I86" t="n">
-        <v>19.89886565532322</v>
+        <v>20.19969060203687</v>
       </c>
       <c r="J86" t="n">
-        <v>83.32649993166598</v>
+        <v>86.7398478793348</v>
       </c>
       <c r="K86" t="n">
         <v>0</v>
@@ -4243,7 +4243,7 @@
         <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>3</v>
+        <v>2.981239892183289</v>
       </c>
     </row>
     <row r="87">
@@ -4251,7 +4251,7 @@
         <v>42232</v>
       </c>
       <c r="B87" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C87" t="n">
         <v>4</v>
@@ -4266,16 +4266,16 @@
         <v>2</v>
       </c>
       <c r="G87" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H87" t="n">
-        <v>9.94943282766161</v>
+        <v>10.69395384813717</v>
       </c>
       <c r="I87" t="n">
-        <v>18.65518655186552</v>
+        <v>20.19969060203687</v>
       </c>
       <c r="J87" t="n">
-        <v>78.35178351783517</v>
+        <v>83.17519659662241</v>
       </c>
       <c r="K87" t="n">
         <v>0</v>
@@ -4287,7 +4287,7 @@
         <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>3</v>
+        <v>2.981239892183289</v>
       </c>
     </row>
     <row r="88">
@@ -4295,7 +4295,7 @@
         <v>42239</v>
       </c>
       <c r="B88" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C88" t="n">
         <v>4</v>
@@ -4304,22 +4304,22 @@
         <v>5</v>
       </c>
       <c r="E88" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F88" t="n">
         <v>2</v>
       </c>
       <c r="G88" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H88" t="n">
-        <v>9.94943282766161</v>
+        <v>10.69395384813717</v>
       </c>
       <c r="I88" t="n">
-        <v>17.41150744840782</v>
+        <v>19.01147350779941</v>
       </c>
       <c r="J88" t="n">
-        <v>78.35178351783517</v>
+        <v>81.98697950238495</v>
       </c>
       <c r="K88" t="n">
         <v>0</v>
@@ -4331,7 +4331,7 @@
         <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>3</v>
+        <v>3.974986522911051</v>
       </c>
     </row>
     <row r="89">
@@ -4339,7 +4339,7 @@
         <v>42246</v>
       </c>
       <c r="B89" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C89" t="n">
         <v>4</v>
@@ -4348,22 +4348,22 @@
         <v>3</v>
       </c>
       <c r="E89" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F89" t="n">
         <v>2</v>
       </c>
       <c r="G89" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H89" t="n">
-        <v>9.94943282766161</v>
+        <v>9.505736753899704</v>
       </c>
       <c r="I89" t="n">
-        <v>19.89886565532322</v>
+        <v>19.01147350779941</v>
       </c>
       <c r="J89" t="n">
-        <v>87.05753724203909</v>
+        <v>86.7398478793348</v>
       </c>
       <c r="K89" t="n">
         <v>0</v>
@@ -4375,7 +4375,7 @@
         <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>3</v>
+        <v>2.981239892183289</v>
       </c>
     </row>
     <row r="90">
@@ -4383,7 +4383,7 @@
         <v>42253</v>
       </c>
       <c r="B90" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C90" t="n">
         <v>4</v>
@@ -4398,16 +4398,16 @@
         <v>2</v>
       </c>
       <c r="G90" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H90" t="n">
-        <v>9.94943282766161</v>
+        <v>9.505736753899704</v>
       </c>
       <c r="I90" t="n">
-        <v>17.41150744840782</v>
+        <v>19.01147350779941</v>
       </c>
       <c r="J90" t="n">
-        <v>93.27593275932759</v>
+        <v>93.86915044475958</v>
       </c>
       <c r="K90" t="n">
         <v>0</v>
@@ -4419,7 +4419,7 @@
         <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>3</v>
+        <v>2.981239892183289</v>
       </c>
     </row>
     <row r="91">
@@ -4427,7 +4427,7 @@
         <v>42260</v>
       </c>
       <c r="B91" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C91" t="n">
         <v>5</v>
@@ -4439,19 +4439,19 @@
         <v>7</v>
       </c>
       <c r="F91" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G91" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H91" t="n">
-        <v>11.19311193111931</v>
+        <v>10.69395384813717</v>
       </c>
       <c r="I91" t="n">
-        <v>21.14254475878092</v>
+        <v>20.19969060203687</v>
       </c>
       <c r="J91" t="n">
-        <v>87.05753724203909</v>
+        <v>87.92806497357226</v>
       </c>
       <c r="K91" t="n">
         <v>0</v>
@@ -4463,7 +4463,7 @@
         <v>0</v>
       </c>
       <c r="N91" t="n">
-        <v>3</v>
+        <v>2.981239892183289</v>
       </c>
     </row>
     <row r="92">
@@ -4486,16 +4486,16 @@
         <v>2</v>
       </c>
       <c r="G92" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H92" t="n">
-        <v>9.94943282766161</v>
+        <v>10.69395384813717</v>
       </c>
       <c r="I92" t="n">
-        <v>19.89886565532322</v>
+        <v>20.19969060203687</v>
       </c>
       <c r="J92" t="n">
-        <v>82.08282082820828</v>
+        <v>81.98697950238495</v>
       </c>
       <c r="K92" t="n">
         <v>0</v>
@@ -4507,7 +4507,7 @@
         <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>3</v>
+        <v>2.981239892183289</v>
       </c>
     </row>
     <row r="93">
@@ -4515,7 +4515,7 @@
         <v>42274</v>
       </c>
       <c r="B93" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C93" t="n">
         <v>5</v>
@@ -4530,16 +4530,16 @@
         <v>2</v>
       </c>
       <c r="G93" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H93" t="n">
-        <v>9.94943282766161</v>
+        <v>9.505736753899704</v>
       </c>
       <c r="I93" t="n">
-        <v>19.89886565532322</v>
+        <v>20.19969060203687</v>
       </c>
       <c r="J93" t="n">
-        <v>82.08282082820828</v>
+        <v>83.17519659662241</v>
       </c>
       <c r="K93" t="n">
         <v>0</v>
@@ -4551,7 +4551,7 @@
         <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>3</v>
+        <v>2.981239892183289</v>
       </c>
     </row>
     <row r="94">
@@ -4559,7 +4559,7 @@
         <v>42281</v>
       </c>
       <c r="B94" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C94" t="n">
         <v>4</v>
@@ -4571,19 +4571,19 @@
         <v>6</v>
       </c>
       <c r="F94" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G94" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H94" t="n">
-        <v>9.94943282766161</v>
+        <v>9.505736753899704</v>
       </c>
       <c r="I94" t="n">
-        <v>18.65518655186552</v>
+        <v>20.19969060203687</v>
       </c>
       <c r="J94" t="n">
-        <v>84.57017903512369</v>
+        <v>86.7398478793348</v>
       </c>
       <c r="K94" t="n">
         <v>0</v>
@@ -4595,7 +4595,7 @@
         <v>0</v>
       </c>
       <c r="N94" t="n">
-        <v>3</v>
+        <v>2.981239892183289</v>
       </c>
     </row>
     <row r="95">
@@ -4618,16 +4618,16 @@
         <v>2</v>
       </c>
       <c r="G95" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H95" t="n">
-        <v>9.94943282766161</v>
+        <v>9.505736753899704</v>
       </c>
       <c r="I95" t="n">
-        <v>18.65518655186552</v>
+        <v>17.82325641356195</v>
       </c>
       <c r="J95" t="n">
-        <v>87.05753724203909</v>
+        <v>87.92806497357226</v>
       </c>
       <c r="K95" t="n">
         <v>0</v>
@@ -4639,7 +4639,7 @@
         <v>0</v>
       </c>
       <c r="N95" t="n">
-        <v>3</v>
+        <v>2.981239892183289</v>
       </c>
     </row>
     <row r="96">
@@ -4647,7 +4647,7 @@
         <v>42295</v>
       </c>
       <c r="B96" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C96" t="n">
         <v>4</v>
@@ -4656,22 +4656,22 @@
         <v>3</v>
       </c>
       <c r="E96" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F96" t="n">
         <v>2</v>
       </c>
       <c r="G96" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H96" t="n">
-        <v>11.19311193111931</v>
+        <v>10.69395384813717</v>
       </c>
       <c r="I96" t="n">
-        <v>19.89886565532322</v>
+        <v>20.19969060203687</v>
       </c>
       <c r="J96" t="n">
-        <v>85.81385813858139</v>
+        <v>85.55163078509733</v>
       </c>
       <c r="K96" t="n">
         <v>0</v>
@@ -4683,7 +4683,7 @@
         <v>0</v>
       </c>
       <c r="N96" t="n">
-        <v>3</v>
+        <v>2.981239892183289</v>
       </c>
     </row>
     <row r="97">
@@ -4691,7 +4691,7 @@
         <v>42302</v>
       </c>
       <c r="B97" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C97" t="n">
         <v>4</v>
@@ -4706,16 +4706,16 @@
         <v>2</v>
       </c>
       <c r="G97" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H97" t="n">
-        <v>11.19311193111931</v>
+        <v>10.69395384813717</v>
       </c>
       <c r="I97" t="n">
-        <v>21.14254475878092</v>
+        <v>21.38790769627433</v>
       </c>
       <c r="J97" t="n">
-        <v>85.81385813858139</v>
+        <v>86.7398478793348</v>
       </c>
       <c r="K97" t="n">
         <v>0</v>
@@ -4727,7 +4727,7 @@
         <v>0</v>
       </c>
       <c r="N97" t="n">
-        <v>3</v>
+        <v>2.981239892183289</v>
       </c>
     </row>
     <row r="98">
@@ -4735,7 +4735,7 @@
         <v>42309</v>
       </c>
       <c r="B98" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C98" t="n">
         <v>4</v>
@@ -4750,16 +4750,16 @@
         <v>2</v>
       </c>
       <c r="G98" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H98" t="n">
-        <v>9.94943282766161</v>
+        <v>10.69395384813717</v>
       </c>
       <c r="I98" t="n">
-        <v>18.65518655186552</v>
+        <v>19.01147350779941</v>
       </c>
       <c r="J98" t="n">
-        <v>82.08282082820828</v>
+        <v>81.98697950238495</v>
       </c>
       <c r="K98" t="n">
         <v>0</v>
@@ -4771,7 +4771,7 @@
         <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>3</v>
+        <v>2.981239892183289</v>
       </c>
     </row>
     <row r="99">
@@ -4794,16 +4794,16 @@
         <v>2</v>
       </c>
       <c r="G99" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H99" t="n">
-        <v>11.19311193111931</v>
+        <v>10.69395384813717</v>
       </c>
       <c r="I99" t="n">
-        <v>18.65518655186552</v>
+        <v>20.19969060203687</v>
       </c>
       <c r="J99" t="n">
-        <v>83.32649993166598</v>
+        <v>81.98697950238495</v>
       </c>
       <c r="K99" t="n">
         <v>0</v>
@@ -4815,7 +4815,7 @@
         <v>0</v>
       </c>
       <c r="N99" t="n">
-        <v>4</v>
+        <v>3.974986522911051</v>
       </c>
     </row>
     <row r="100">
@@ -4823,7 +4823,7 @@
         <v>42323</v>
       </c>
       <c r="B100" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C100" t="n">
         <v>5</v>
@@ -4832,22 +4832,22 @@
         <v>4</v>
       </c>
       <c r="E100" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F100" t="n">
         <v>2</v>
       </c>
       <c r="G100" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H100" t="n">
-        <v>11.19311193111931</v>
+        <v>10.69395384813717</v>
       </c>
       <c r="I100" t="n">
-        <v>19.89886565532322</v>
+        <v>20.19969060203687</v>
       </c>
       <c r="J100" t="n">
-        <v>85.81385813858139</v>
+        <v>85.55163078509733</v>
       </c>
       <c r="K100" t="n">
         <v>0</v>
@@ -4859,7 +4859,7 @@
         <v>0</v>
       </c>
       <c r="N100" t="n">
-        <v>4</v>
+        <v>3.974986522911051</v>
       </c>
     </row>
     <row r="101">
@@ -4867,7 +4867,7 @@
         <v>42330</v>
       </c>
       <c r="B101" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C101" t="n">
         <v>4</v>
@@ -4882,16 +4882,16 @@
         <v>2</v>
       </c>
       <c r="G101" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H101" t="n">
-        <v>9.94943282766161</v>
+        <v>9.505736753899704</v>
       </c>
       <c r="I101" t="n">
-        <v>18.65518655186552</v>
+        <v>19.01147350779941</v>
       </c>
       <c r="J101" t="n">
-        <v>74.62074620746208</v>
+        <v>76.04589403119763</v>
       </c>
       <c r="K101" t="n">
         <v>0</v>
@@ -4903,7 +4903,7 @@
         <v>0</v>
       </c>
       <c r="N101" t="n">
-        <v>3</v>
+        <v>2.981239892183289</v>
       </c>
     </row>
     <row r="102">
@@ -4911,7 +4911,7 @@
         <v>42337</v>
       </c>
       <c r="B102" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C102" t="n">
         <v>4</v>
@@ -4926,16 +4926,16 @@
         <v>2</v>
       </c>
       <c r="G102" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H102" t="n">
-        <v>9.94943282766161</v>
+        <v>9.505736753899704</v>
       </c>
       <c r="I102" t="n">
-        <v>18.65518655186552</v>
+        <v>17.82325641356195</v>
       </c>
       <c r="J102" t="n">
-        <v>73.37706710400437</v>
+        <v>78.42232821967256</v>
       </c>
       <c r="K102" t="n">
         <v>0</v>
@@ -4947,7 +4947,7 @@
         <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>3</v>
+        <v>2.981239892183289</v>
       </c>
     </row>
     <row r="103">
@@ -4955,7 +4955,7 @@
         <v>42344</v>
       </c>
       <c r="B103" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C103" t="n">
         <v>4</v>
@@ -4970,16 +4970,16 @@
         <v>2</v>
       </c>
       <c r="G103" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H103" t="n">
-        <v>8.705753724203909</v>
+        <v>9.505736753899704</v>
       </c>
       <c r="I103" t="n">
-        <v>21.14254475878092</v>
+        <v>21.38790769627433</v>
       </c>
       <c r="J103" t="n">
-        <v>73.37706710400437</v>
+        <v>72.48124274848524</v>
       </c>
       <c r="K103" t="n">
         <v>0</v>
@@ -4991,7 +4991,7 @@
         <v>0</v>
       </c>
       <c r="N103" t="n">
-        <v>3</v>
+        <v>2.981239892183289</v>
       </c>
     </row>
     <row r="104">
@@ -4999,7 +4999,7 @@
         <v>42351</v>
       </c>
       <c r="B104" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C104" t="n">
         <v>4</v>
@@ -5014,16 +5014,16 @@
         <v>2</v>
       </c>
       <c r="G104" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H104" t="n">
-        <v>9.94943282766161</v>
+        <v>9.505736753899704</v>
       </c>
       <c r="I104" t="n">
-        <v>17.41150744840782</v>
+        <v>17.82325641356195</v>
       </c>
       <c r="J104" t="n">
-        <v>75.86442531091978</v>
+        <v>77.23411112543509</v>
       </c>
       <c r="K104" t="n">
         <v>0</v>
@@ -5035,7 +5035,7 @@
         <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>3</v>
+        <v>2.981239892183289</v>
       </c>
     </row>
     <row r="105">
@@ -5058,16 +5058,16 @@
         <v>2</v>
       </c>
       <c r="G105" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H105" t="n">
-        <v>9.94943282766161</v>
+        <v>10.69395384813717</v>
       </c>
       <c r="I105" t="n">
-        <v>23.62990296569632</v>
+        <v>23.76434188474926</v>
       </c>
       <c r="J105" t="n">
-        <v>68.40235069017356</v>
+        <v>68.91659146577285</v>
       </c>
       <c r="K105" t="n">
         <v>0</v>
@@ -5079,7 +5079,7 @@
         <v>0</v>
       </c>
       <c r="N105" t="n">
-        <v>3</v>
+        <v>2.981239892183289</v>
       </c>
     </row>
     <row r="106">
@@ -5087,7 +5087,7 @@
         <v>42365</v>
       </c>
       <c r="B106" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C106" t="n">
         <v>3</v>
@@ -5102,16 +5102,16 @@
         <v>2</v>
       </c>
       <c r="G106" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H106" t="n">
-        <v>9.94943282766161</v>
+        <v>9.505736753899704</v>
       </c>
       <c r="I106" t="n">
-        <v>26.11726117261173</v>
+        <v>26.14077607322419</v>
       </c>
       <c r="J106" t="n">
-        <v>72.13338800054667</v>
+        <v>71.29302565424778</v>
       </c>
       <c r="K106" t="n">
         <v>0</v>
@@ -5123,7 +5123,7 @@
         <v>0</v>
       </c>
       <c r="N106" t="n">
-        <v>2</v>
+        <v>1.987493261455526</v>
       </c>
     </row>
     <row r="107">
@@ -5131,7 +5131,7 @@
         <v>42372</v>
       </c>
       <c r="B107" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C107" t="n">
         <v>4</v>
@@ -5146,16 +5146,16 @@
         <v>2</v>
       </c>
       <c r="G107" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H107" t="n">
-        <v>9.94943282766161</v>
+        <v>9.505736753899704</v>
       </c>
       <c r="I107" t="n">
-        <v>21.14254475878092</v>
+        <v>22.5761247905118</v>
       </c>
       <c r="J107" t="n">
-        <v>77.10810441437748</v>
+        <v>76.04589403119763</v>
       </c>
       <c r="K107" t="n">
         <v>0</v>
@@ -5167,7 +5167,7 @@
         <v>0</v>
       </c>
       <c r="N107" t="n">
-        <v>2</v>
+        <v>1.987493261455526</v>
       </c>
     </row>
     <row r="108">
@@ -5175,7 +5175,7 @@
         <v>42379</v>
       </c>
       <c r="B108" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C108" t="n">
         <v>4</v>
@@ -5190,16 +5190,16 @@
         <v>2</v>
       </c>
       <c r="G108" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H108" t="n">
-        <v>9.94943282766161</v>
+        <v>9.505736753899704</v>
       </c>
       <c r="I108" t="n">
-        <v>18.65518655186552</v>
+        <v>19.01147350779941</v>
       </c>
       <c r="J108" t="n">
-        <v>80.83914172475059</v>
+        <v>80.79876240814748</v>
       </c>
       <c r="K108" t="n">
         <v>0</v>
@@ -5211,7 +5211,7 @@
         <v>0</v>
       </c>
       <c r="N108" t="n">
-        <v>2</v>
+        <v>1.987493261455526</v>
       </c>
     </row>
     <row r="109">
@@ -5219,7 +5219,7 @@
         <v>42386</v>
       </c>
       <c r="B109" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C109" t="n">
         <v>4</v>
@@ -5234,16 +5234,16 @@
         <v>2</v>
       </c>
       <c r="G109" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H109" t="n">
-        <v>11.19311193111931</v>
+        <v>9.505736753899704</v>
       </c>
       <c r="I109" t="n">
-        <v>18.65518655186552</v>
+        <v>19.01147350779941</v>
       </c>
       <c r="J109" t="n">
-        <v>77.10810441437748</v>
+        <v>80.79876240814748</v>
       </c>
       <c r="K109" t="n">
         <v>0</v>
@@ -5255,7 +5255,7 @@
         <v>0</v>
       </c>
       <c r="N109" t="n">
-        <v>2</v>
+        <v>1.987493261455526</v>
       </c>
     </row>
     <row r="110">
@@ -5278,16 +5278,16 @@
         <v>2</v>
       </c>
       <c r="G110" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H110" t="n">
-        <v>9.94943282766161</v>
+        <v>10.69395384813717</v>
       </c>
       <c r="I110" t="n">
-        <v>19.89886565532322</v>
+        <v>19.01147350779941</v>
       </c>
       <c r="J110" t="n">
-        <v>85.81385813858139</v>
+        <v>84.36341369085987</v>
       </c>
       <c r="K110" t="n">
         <v>0</v>
@@ -5299,7 +5299,7 @@
         <v>0</v>
       </c>
       <c r="N110" t="n">
-        <v>2</v>
+        <v>1.987493261455526</v>
       </c>
     </row>
     <row r="111">
@@ -5310,7 +5310,7 @@
         <v>52</v>
       </c>
       <c r="C111" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D111" t="n">
         <v>3</v>
@@ -5322,16 +5322,16 @@
         <v>2</v>
       </c>
       <c r="G111" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H111" t="n">
-        <v>9.94943282766161</v>
+        <v>10.69395384813717</v>
       </c>
       <c r="I111" t="n">
-        <v>19.89886565532322</v>
+        <v>20.19969060203687</v>
       </c>
       <c r="J111" t="n">
-        <v>82.08282082820828</v>
+        <v>83.17519659662241</v>
       </c>
       <c r="K111" t="n">
         <v>0</v>
@@ -5343,7 +5343,7 @@
         <v>0</v>
       </c>
       <c r="N111" t="n">
-        <v>2</v>
+        <v>1.987493261455526</v>
       </c>
     </row>
     <row r="112">
@@ -5351,7 +5351,7 @@
         <v>42407</v>
       </c>
       <c r="B112" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C112" t="n">
         <v>4</v>
@@ -5366,16 +5366,16 @@
         <v>2</v>
       </c>
       <c r="G112" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H112" t="n">
-        <v>9.94943282766161</v>
+        <v>10.69395384813717</v>
       </c>
       <c r="I112" t="n">
-        <v>19.89886565532322</v>
+        <v>21.38790769627433</v>
       </c>
       <c r="J112" t="n">
-        <v>78.35178351783517</v>
+        <v>79.61054531391002</v>
       </c>
       <c r="K112" t="n">
         <v>0</v>
@@ -5387,7 +5387,7 @@
         <v>0</v>
       </c>
       <c r="N112" t="n">
-        <v>2</v>
+        <v>1.987493261455526</v>
       </c>
     </row>
     <row r="113">
@@ -5395,10 +5395,10 @@
         <v>42414</v>
       </c>
       <c r="B113" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C113" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D113" t="n">
         <v>2</v>
@@ -5410,16 +5410,16 @@
         <v>2</v>
       </c>
       <c r="G113" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H113" t="n">
-        <v>9.94943282766161</v>
+        <v>9.505736753899704</v>
       </c>
       <c r="I113" t="n">
-        <v>19.89886565532322</v>
+        <v>20.19969060203687</v>
       </c>
       <c r="J113" t="n">
-        <v>80.83914172475059</v>
+        <v>81.98697950238495</v>
       </c>
       <c r="K113" t="n">
         <v>0</v>
@@ -5431,7 +5431,7 @@
         <v>0</v>
       </c>
       <c r="N113" t="n">
-        <v>2</v>
+        <v>1.987493261455526</v>
       </c>
     </row>
     <row r="114">
@@ -5439,7 +5439,7 @@
         <v>42421</v>
       </c>
       <c r="B114" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C114" t="n">
         <v>3</v>
@@ -5454,16 +5454,16 @@
         <v>2</v>
       </c>
       <c r="G114" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H114" t="n">
-        <v>9.94943282766161</v>
+        <v>9.505736753899704</v>
       </c>
       <c r="I114" t="n">
-        <v>19.89886565532322</v>
+        <v>20.19969060203687</v>
       </c>
       <c r="J114" t="n">
-        <v>77.10810441437748</v>
+        <v>78.42232821967256</v>
       </c>
       <c r="K114" t="n">
         <v>0</v>
@@ -5475,7 +5475,7 @@
         <v>0</v>
       </c>
       <c r="N114" t="n">
-        <v>2</v>
+        <v>1.987493261455526</v>
       </c>
     </row>
     <row r="115">
@@ -5483,7 +5483,7 @@
         <v>42428</v>
       </c>
       <c r="B115" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C115" t="n">
         <v>4</v>
@@ -5498,16 +5498,16 @@
         <v>2</v>
       </c>
       <c r="G115" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H115" t="n">
-        <v>9.94943282766161</v>
+        <v>9.505736753899704</v>
       </c>
       <c r="I115" t="n">
-        <v>19.89886565532322</v>
+        <v>19.01147350779941</v>
       </c>
       <c r="J115" t="n">
-        <v>74.62074620746208</v>
+        <v>76.04589403119763</v>
       </c>
       <c r="K115" t="n">
         <v>0</v>
@@ -5519,7 +5519,7 @@
         <v>0</v>
       </c>
       <c r="N115" t="n">
-        <v>2</v>
+        <v>1.987493261455526</v>
       </c>
     </row>
     <row r="116">
@@ -5542,16 +5542,16 @@
         <v>2</v>
       </c>
       <c r="G116" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H116" t="n">
-        <v>8.705753724203909</v>
+        <v>9.505736753899704</v>
       </c>
       <c r="I116" t="n">
-        <v>18.65518655186552</v>
+        <v>19.01147350779941</v>
       </c>
       <c r="J116" t="n">
-        <v>74.62074620746208</v>
+        <v>74.85767693696017</v>
       </c>
       <c r="K116" t="n">
         <v>0</v>
@@ -5563,7 +5563,7 @@
         <v>0</v>
       </c>
       <c r="N116" t="n">
-        <v>2</v>
+        <v>1.987493261455526</v>
       </c>
     </row>
     <row r="117">
@@ -5574,7 +5574,7 @@
         <v>56</v>
       </c>
       <c r="C117" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D117" t="n">
         <v>2</v>
@@ -5586,16 +5586,16 @@
         <v>2</v>
       </c>
       <c r="G117" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H117" t="n">
-        <v>9.94943282766161</v>
+        <v>9.505736753899704</v>
       </c>
       <c r="I117" t="n">
-        <v>18.65518655186552</v>
+        <v>17.82325641356195</v>
       </c>
       <c r="J117" t="n">
-        <v>78.35178351783517</v>
+        <v>76.04589403119763</v>
       </c>
       <c r="K117" t="n">
         <v>0</v>
@@ -5607,7 +5607,7 @@
         <v>0</v>
       </c>
       <c r="N117" t="n">
-        <v>2</v>
+        <v>1.987493261455526</v>
       </c>
     </row>
     <row r="118">
@@ -5615,7 +5615,7 @@
         <v>42449</v>
       </c>
       <c r="B118" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C118" t="n">
         <v>4</v>
@@ -5630,16 +5630,16 @@
         <v>2</v>
       </c>
       <c r="G118" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H118" t="n">
-        <v>11.19311193111931</v>
+        <v>10.69395384813717</v>
       </c>
       <c r="I118" t="n">
-        <v>21.14254475878092</v>
+        <v>21.38790769627433</v>
       </c>
       <c r="J118" t="n">
-        <v>85.81385813858139</v>
+        <v>83.17519659662241</v>
       </c>
       <c r="K118" t="n">
         <v>0</v>
@@ -5651,7 +5651,7 @@
         <v>0</v>
       </c>
       <c r="N118" t="n">
-        <v>3</v>
+        <v>2.981239892183289</v>
       </c>
     </row>
     <row r="119">
@@ -5659,7 +5659,7 @@
         <v>42456</v>
       </c>
       <c r="B119" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C119" t="n">
         <v>3</v>
@@ -5674,16 +5674,16 @@
         <v>2</v>
       </c>
       <c r="G119" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H119" t="n">
-        <v>11.19311193111931</v>
+        <v>9.505736753899704</v>
       </c>
       <c r="I119" t="n">
-        <v>21.14254475878092</v>
+        <v>21.38790769627433</v>
       </c>
       <c r="J119" t="n">
-        <v>85.81385813858139</v>
+        <v>84.36341369085987</v>
       </c>
       <c r="K119" t="n">
         <v>0</v>
@@ -5695,7 +5695,7 @@
         <v>0</v>
       </c>
       <c r="N119" t="n">
-        <v>2</v>
+        <v>1.987493261455526</v>
       </c>
     </row>
     <row r="120">
@@ -5703,7 +5703,7 @@
         <v>42463</v>
       </c>
       <c r="B120" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C120" t="n">
         <v>4</v>
@@ -5718,16 +5718,16 @@
         <v>2</v>
       </c>
       <c r="G120" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H120" t="n">
-        <v>11.19311193111931</v>
+        <v>10.69395384813717</v>
       </c>
       <c r="I120" t="n">
-        <v>19.89886565532322</v>
+        <v>21.38790769627433</v>
       </c>
       <c r="J120" t="n">
-        <v>78.35178351783517</v>
+        <v>78.42232821967256</v>
       </c>
       <c r="K120" t="n">
         <v>0</v>
@@ -5739,7 +5739,7 @@
         <v>0</v>
       </c>
       <c r="N120" t="n">
-        <v>2</v>
+        <v>1.987493261455526</v>
       </c>
     </row>
     <row r="121">
@@ -5747,7 +5747,7 @@
         <v>42470</v>
       </c>
       <c r="B121" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C121" t="n">
         <v>4</v>
@@ -5756,22 +5756,22 @@
         <v>2</v>
       </c>
       <c r="E121" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F121" t="n">
         <v>2</v>
       </c>
       <c r="G121" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H121" t="n">
-        <v>9.94943282766161</v>
+        <v>10.69395384813717</v>
       </c>
       <c r="I121" t="n">
-        <v>19.89886565532322</v>
+        <v>20.19969060203687</v>
       </c>
       <c r="J121" t="n">
-        <v>80.83914172475059</v>
+        <v>83.17519659662241</v>
       </c>
       <c r="K121" t="n">
         <v>0</v>
@@ -5783,7 +5783,7 @@
         <v>0</v>
       </c>
       <c r="N121" t="n">
-        <v>2</v>
+        <v>1.987493261455526</v>
       </c>
     </row>
     <row r="122">
@@ -5791,7 +5791,7 @@
         <v>42477</v>
       </c>
       <c r="B122" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C122" t="n">
         <v>4</v>
@@ -5806,16 +5806,16 @@
         <v>2</v>
       </c>
       <c r="G122" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H122" t="n">
-        <v>9.94943282766161</v>
+        <v>9.505736753899704</v>
       </c>
       <c r="I122" t="n">
-        <v>19.89886565532322</v>
+        <v>20.19969060203687</v>
       </c>
       <c r="J122" t="n">
-        <v>80.83914172475059</v>
+        <v>84.36341369085987</v>
       </c>
       <c r="K122" t="n">
         <v>0</v>
@@ -5827,7 +5827,7 @@
         <v>0</v>
       </c>
       <c r="N122" t="n">
-        <v>2</v>
+        <v>1.987493261455526</v>
       </c>
     </row>
     <row r="123">
@@ -5835,28 +5835,28 @@
         <v>42484</v>
       </c>
       <c r="B123" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C123" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D123" t="n">
         <v>3</v>
       </c>
       <c r="E123" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F123" t="n">
         <v>3</v>
       </c>
       <c r="G123" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H123" t="n">
-        <v>12.43679103457701</v>
+        <v>11.88217094237463</v>
       </c>
       <c r="I123" t="n">
-        <v>23.62990296569632</v>
+        <v>23.76434188474926</v>
       </c>
       <c r="J123" t="n">
         <v>100</v>
@@ -5871,7 +5871,7 @@
         <v>0</v>
       </c>
       <c r="N123" t="n">
-        <v>3</v>
+        <v>2.981239892183289</v>
       </c>
     </row>
     <row r="124">
@@ -5894,16 +5894,16 @@
         <v>2</v>
       </c>
       <c r="G124" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H124" t="n">
-        <v>9.94943282766161</v>
+        <v>9.505736753899704</v>
       </c>
       <c r="I124" t="n">
-        <v>21.14254475878092</v>
+        <v>23.76434188474926</v>
       </c>
       <c r="J124" t="n">
-        <v>80.83914172475059</v>
+        <v>79.61054531391002</v>
       </c>
       <c r="K124" t="n">
         <v>0</v>
@@ -5915,7 +5915,7 @@
         <v>0</v>
       </c>
       <c r="N124" t="n">
-        <v>2</v>
+        <v>1.987493261455526</v>
       </c>
     </row>
     <row r="125">
@@ -5923,7 +5923,7 @@
         <v>42498</v>
       </c>
       <c r="B125" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C125" t="n">
         <v>4</v>
@@ -5938,16 +5938,16 @@
         <v>2</v>
       </c>
       <c r="G125" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H125" t="n">
-        <v>9.94943282766161</v>
+        <v>10.69395384813717</v>
       </c>
       <c r="I125" t="n">
-        <v>19.89886565532322</v>
+        <v>21.38790769627433</v>
       </c>
       <c r="J125" t="n">
-        <v>88.30121634549678</v>
+        <v>80.79876240814748</v>
       </c>
       <c r="K125" t="n">
         <v>0</v>
@@ -5959,7 +5959,7 @@
         <v>0</v>
       </c>
       <c r="N125" t="n">
-        <v>2</v>
+        <v>1.987493261455526</v>
       </c>
     </row>
     <row r="126">
@@ -5967,7 +5967,7 @@
         <v>42505</v>
       </c>
       <c r="B126" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C126" t="n">
         <v>4</v>
@@ -5982,16 +5982,16 @@
         <v>2</v>
       </c>
       <c r="G126" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H126" t="n">
-        <v>9.94943282766161</v>
+        <v>10.69395384813717</v>
       </c>
       <c r="I126" t="n">
-        <v>24.87358206915403</v>
+        <v>23.76434188474926</v>
       </c>
       <c r="J126" t="n">
-        <v>83.32649993166598</v>
+        <v>85.55163078509733</v>
       </c>
       <c r="K126" t="n">
         <v>0</v>
@@ -6003,7 +6003,7 @@
         <v>0</v>
       </c>
       <c r="N126" t="n">
-        <v>3</v>
+        <v>2.981239892183289</v>
       </c>
     </row>
     <row r="127">
@@ -6026,13 +6026,13 @@
         <v>4</v>
       </c>
       <c r="G127" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H127" t="n">
-        <v>12.43679103457701</v>
+        <v>13.07038803661209</v>
       </c>
       <c r="I127" t="n">
-        <v>27.36094027606943</v>
+        <v>26.14077607322419</v>
       </c>
       <c r="J127" t="n">
         <v>100</v>
@@ -6047,7 +6047,7 @@
         <v>0</v>
       </c>
       <c r="N127" t="n">
-        <v>4</v>
+        <v>3.974986522911051</v>
       </c>
     </row>
     <row r="128">
@@ -6055,7 +6055,7 @@
         <v>42519</v>
       </c>
       <c r="B128" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C128" t="n">
         <v>4</v>
@@ -6070,16 +6070,16 @@
         <v>2</v>
       </c>
       <c r="G128" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H128" t="n">
-        <v>9.94943282766161</v>
+        <v>10.69395384813717</v>
       </c>
       <c r="I128" t="n">
-        <v>22.38622386223862</v>
+        <v>22.5761247905118</v>
       </c>
       <c r="J128" t="n">
-        <v>88.30121634549678</v>
+        <v>90.30449916204719</v>
       </c>
       <c r="K128" t="n">
         <v>0</v>
@@ -6091,7 +6091,7 @@
         <v>0</v>
       </c>
       <c r="N128" t="n">
-        <v>3</v>
+        <v>2.981239892183289</v>
       </c>
     </row>
     <row r="129">
@@ -6114,16 +6114,16 @@
         <v>2</v>
       </c>
       <c r="G129" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H129" t="n">
-        <v>11.19311193111931</v>
+        <v>10.69395384813717</v>
       </c>
       <c r="I129" t="n">
-        <v>21.14254475878092</v>
+        <v>21.38790769627433</v>
       </c>
       <c r="J129" t="n">
-        <v>84.57017903512369</v>
+        <v>81.98697950238495</v>
       </c>
       <c r="K129" t="n">
         <v>0</v>
@@ -6135,7 +6135,7 @@
         <v>0</v>
       </c>
       <c r="N129" t="n">
-        <v>2</v>
+        <v>2.981239892183289</v>
       </c>
     </row>
     <row r="130">
@@ -6143,7 +6143,7 @@
         <v>42533</v>
       </c>
       <c r="B130" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C130" t="n">
         <v>4</v>
@@ -6158,13 +6158,13 @@
         <v>2</v>
       </c>
       <c r="G130" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H130" t="n">
-        <v>9.94943282766161</v>
+        <v>10.69395384813717</v>
       </c>
       <c r="I130" t="n">
-        <v>26.11726117261173</v>
+        <v>27.32899316746165</v>
       </c>
       <c r="J130" t="n">
         <v>100</v>
@@ -6179,7 +6179,7 @@
         <v>0</v>
       </c>
       <c r="N130" t="n">
-        <v>3</v>
+        <v>2.981239892183289</v>
       </c>
     </row>
     <row r="131">
@@ -6187,7 +6187,7 @@
         <v>42540</v>
       </c>
       <c r="B131" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C131" t="n">
         <v>5</v>
@@ -6202,16 +6202,16 @@
         <v>2</v>
       </c>
       <c r="G131" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H131" t="n">
-        <v>9.94943282766161</v>
+        <v>10.69395384813717</v>
       </c>
       <c r="I131" t="n">
-        <v>27.36094027606943</v>
+        <v>27.32899316746165</v>
       </c>
       <c r="J131" t="n">
-        <v>95.76329096624301</v>
+        <v>93.86915044475958</v>
       </c>
       <c r="K131" t="n">
         <v>0</v>
@@ -6223,7 +6223,7 @@
         <v>0</v>
       </c>
       <c r="N131" t="n">
-        <v>3</v>
+        <v>2.981239892183289</v>
       </c>
     </row>
     <row r="132">
@@ -6234,7 +6234,7 @@
         <v>80</v>
       </c>
       <c r="C132" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D132" t="n">
         <v>3</v>
@@ -6246,16 +6246,16 @@
         <v>2</v>
       </c>
       <c r="G132" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H132" t="n">
-        <v>11.19311193111931</v>
+        <v>10.69395384813717</v>
       </c>
       <c r="I132" t="n">
-        <v>26.11726117261173</v>
+        <v>26.14077607322419</v>
       </c>
       <c r="J132" t="n">
-        <v>75.86442531091978</v>
+        <v>77.23411112543509</v>
       </c>
       <c r="K132" t="n">
         <v>0</v>
@@ -6267,7 +6267,7 @@
         <v>0</v>
       </c>
       <c r="N132" t="n">
-        <v>3</v>
+        <v>2.981239892183289</v>
       </c>
     </row>
     <row r="133">
@@ -6275,7 +6275,7 @@
         <v>42554</v>
       </c>
       <c r="B133" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C133" t="n">
         <v>4</v>
@@ -6290,16 +6290,16 @@
         <v>2</v>
       </c>
       <c r="G133" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H133" t="n">
-        <v>11.19311193111931</v>
+        <v>10.69395384813717</v>
       </c>
       <c r="I133" t="n">
-        <v>22.38622386223862</v>
+        <v>22.5761247905118</v>
       </c>
       <c r="J133" t="n">
-        <v>78.35178351783517</v>
+        <v>79.61054531391002</v>
       </c>
       <c r="K133" t="n">
         <v>0</v>
@@ -6311,7 +6311,7 @@
         <v>0</v>
       </c>
       <c r="N133" t="n">
-        <v>2</v>
+        <v>1.987493261455526</v>
       </c>
     </row>
     <row r="134">
@@ -6334,16 +6334,16 @@
         <v>2</v>
       </c>
       <c r="G134" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H134" t="n">
-        <v>11.19311193111931</v>
+        <v>11.88217094237463</v>
       </c>
       <c r="I134" t="n">
-        <v>22.38622386223862</v>
+        <v>23.76434188474926</v>
       </c>
       <c r="J134" t="n">
-        <v>90.7885745524122</v>
+        <v>91.49271625628465</v>
       </c>
       <c r="K134" t="n">
         <v>0</v>
@@ -6355,7 +6355,7 @@
         <v>0</v>
       </c>
       <c r="N134" t="n">
-        <v>3</v>
+        <v>2.981239892183289</v>
       </c>
     </row>
     <row r="135">
@@ -6363,7 +6363,7 @@
         <v>42568</v>
       </c>
       <c r="B135" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C135" t="n">
         <v>4</v>
@@ -6378,16 +6378,16 @@
         <v>2</v>
       </c>
       <c r="G135" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H135" t="n">
-        <v>12.43679103457701</v>
+        <v>13.07038803661209</v>
       </c>
       <c r="I135" t="n">
-        <v>22.38622386223862</v>
+        <v>23.76434188474926</v>
       </c>
       <c r="J135" t="n">
-        <v>75.86442531091978</v>
+        <v>77.23411112543509</v>
       </c>
       <c r="K135" t="n">
         <v>0</v>
@@ -6399,7 +6399,7 @@
         <v>0</v>
       </c>
       <c r="N135" t="n">
-        <v>3</v>
+        <v>2.981239892183289</v>
       </c>
     </row>
     <row r="136">
@@ -6407,7 +6407,7 @@
         <v>42575</v>
       </c>
       <c r="B136" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C136" t="n">
         <v>4</v>
@@ -6422,16 +6422,16 @@
         <v>2</v>
       </c>
       <c r="G136" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H136" t="n">
-        <v>11.19311193111931</v>
+        <v>11.88217094237463</v>
       </c>
       <c r="I136" t="n">
-        <v>22.38622386223862</v>
+        <v>22.5761247905118</v>
       </c>
       <c r="J136" t="n">
-        <v>78.35178351783517</v>
+        <v>76.04589403119763</v>
       </c>
       <c r="K136" t="n">
         <v>0</v>
@@ -6443,7 +6443,7 @@
         <v>0</v>
       </c>
       <c r="N136" t="n">
-        <v>3</v>
+        <v>2.981239892183289</v>
       </c>
     </row>
     <row r="137">
@@ -6466,16 +6466,16 @@
         <v>2</v>
       </c>
       <c r="G137" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H137" t="n">
-        <v>11.19311193111931</v>
+        <v>11.88217094237463</v>
       </c>
       <c r="I137" t="n">
-        <v>22.38622386223862</v>
+        <v>22.5761247905118</v>
       </c>
       <c r="J137" t="n">
-        <v>77.10810441437748</v>
+        <v>77.23411112543509</v>
       </c>
       <c r="K137" t="n">
         <v>0</v>
@@ -6487,7 +6487,7 @@
         <v>0</v>
       </c>
       <c r="N137" t="n">
-        <v>3</v>
+        <v>2.981239892183289</v>
       </c>
     </row>
     <row r="138">
@@ -6495,10 +6495,10 @@
         <v>42589</v>
       </c>
       <c r="B138" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C138" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D138" t="n">
         <v>3</v>
@@ -6510,16 +6510,16 @@
         <v>2</v>
       </c>
       <c r="G138" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H138" t="n">
-        <v>9.94943282766161</v>
+        <v>10.69395384813717</v>
       </c>
       <c r="I138" t="n">
-        <v>19.89886565532322</v>
+        <v>19.01147350779941</v>
       </c>
       <c r="J138" t="n">
-        <v>77.10810441437748</v>
+        <v>77.23411112543509</v>
       </c>
       <c r="K138" t="n">
         <v>0</v>
@@ -6531,7 +6531,7 @@
         <v>0</v>
       </c>
       <c r="N138" t="n">
-        <v>3</v>
+        <v>2.981239892183289</v>
       </c>
     </row>
     <row r="139">
@@ -6539,7 +6539,7 @@
         <v>42596</v>
       </c>
       <c r="B139" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C139" t="n">
         <v>3</v>
@@ -6554,16 +6554,16 @@
         <v>2</v>
       </c>
       <c r="G139" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H139" t="n">
-        <v>11.19311193111931</v>
+        <v>10.69395384813717</v>
       </c>
       <c r="I139" t="n">
-        <v>23.62990296569632</v>
+        <v>24.95255897898672</v>
       </c>
       <c r="J139" t="n">
-        <v>75.86442531091978</v>
+        <v>77.23411112543509</v>
       </c>
       <c r="K139" t="n">
         <v>0</v>
@@ -6575,7 +6575,7 @@
         <v>0</v>
       </c>
       <c r="N139" t="n">
-        <v>2</v>
+        <v>1.987493261455526</v>
       </c>
     </row>
     <row r="140">
@@ -6598,16 +6598,16 @@
         <v>2</v>
       </c>
       <c r="G140" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H140" t="n">
-        <v>9.94943282766161</v>
+        <v>9.505736753899704</v>
       </c>
       <c r="I140" t="n">
-        <v>21.14254475878092</v>
+        <v>21.38790769627433</v>
       </c>
       <c r="J140" t="n">
-        <v>77.10810441437748</v>
+        <v>74.85767693696017</v>
       </c>
       <c r="K140" t="n">
         <v>0</v>
@@ -6619,7 +6619,7 @@
         <v>0</v>
       </c>
       <c r="N140" t="n">
-        <v>3</v>
+        <v>2.981239892183289</v>
       </c>
     </row>
     <row r="141">
@@ -6627,7 +6627,7 @@
         <v>42610</v>
       </c>
       <c r="B141" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C141" t="n">
         <v>3</v>
@@ -6642,16 +6642,16 @@
         <v>2</v>
       </c>
       <c r="G141" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H141" t="n">
-        <v>9.94943282766161</v>
+        <v>10.69395384813717</v>
       </c>
       <c r="I141" t="n">
-        <v>21.14254475878092</v>
+        <v>21.38790769627433</v>
       </c>
       <c r="J141" t="n">
-        <v>77.10810441437748</v>
+        <v>77.23411112543509</v>
       </c>
       <c r="K141" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
         <v>0</v>
       </c>
       <c r="N141" t="n">
-        <v>2</v>
+        <v>1.987493261455526</v>
       </c>
     </row>
     <row r="142">
@@ -6671,7 +6671,7 @@
         <v>42617</v>
       </c>
       <c r="B142" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C142" t="n">
         <v>4</v>
@@ -6686,16 +6686,16 @@
         <v>2</v>
       </c>
       <c r="G142" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H142" t="n">
-        <v>11.19311193111931</v>
+        <v>9.505736753899704</v>
       </c>
       <c r="I142" t="n">
-        <v>22.38622386223862</v>
+        <v>22.5761247905118</v>
       </c>
       <c r="J142" t="n">
-        <v>79.59546262129288</v>
+        <v>78.42232821967256</v>
       </c>
       <c r="K142" t="n">
         <v>0</v>
@@ -6707,7 +6707,7 @@
         <v>0</v>
       </c>
       <c r="N142" t="n">
-        <v>3</v>
+        <v>2.981239892183289</v>
       </c>
     </row>
     <row r="143">
@@ -6715,10 +6715,10 @@
         <v>42624</v>
       </c>
       <c r="B143" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C143" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D143" t="n">
         <v>3</v>
@@ -6730,16 +6730,16 @@
         <v>2</v>
       </c>
       <c r="G143" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H143" t="n">
-        <v>9.94943282766161</v>
+        <v>9.505736753899704</v>
       </c>
       <c r="I143" t="n">
-        <v>22.38622386223862</v>
+        <v>21.38790769627433</v>
       </c>
       <c r="J143" t="n">
-        <v>75.86442531091978</v>
+        <v>76.04589403119763</v>
       </c>
       <c r="K143" t="n">
         <v>0</v>
@@ -6751,7 +6751,7 @@
         <v>0</v>
       </c>
       <c r="N143" t="n">
-        <v>2</v>
+        <v>2.981239892183289</v>
       </c>
     </row>
     <row r="144">
@@ -6759,7 +6759,7 @@
         <v>42631</v>
       </c>
       <c r="B144" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C144" t="n">
         <v>4</v>
@@ -6774,16 +6774,16 @@
         <v>2</v>
       </c>
       <c r="G144" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H144" t="n">
-        <v>12.43679103457701</v>
+        <v>10.69395384813717</v>
       </c>
       <c r="I144" t="n">
-        <v>21.14254475878092</v>
+        <v>21.38790769627433</v>
       </c>
       <c r="J144" t="n">
-        <v>75.86442531091978</v>
+        <v>77.23411112543509</v>
       </c>
       <c r="K144" t="n">
         <v>0</v>
@@ -6795,7 +6795,7 @@
         <v>0</v>
       </c>
       <c r="N144" t="n">
-        <v>2</v>
+        <v>2.981239892183289</v>
       </c>
     </row>
     <row r="145">
@@ -6803,7 +6803,7 @@
         <v>42638</v>
       </c>
       <c r="B145" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C145" t="n">
         <v>4</v>
@@ -6812,22 +6812,22 @@
         <v>3</v>
       </c>
       <c r="E145" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F145" t="n">
         <v>2</v>
       </c>
       <c r="G145" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H145" t="n">
-        <v>9.94943282766161</v>
+        <v>10.69395384813717</v>
       </c>
       <c r="I145" t="n">
-        <v>22.38622386223862</v>
+        <v>22.5761247905118</v>
       </c>
       <c r="J145" t="n">
-        <v>75.86442531091978</v>
+        <v>77.23411112543509</v>
       </c>
       <c r="K145" t="n">
         <v>0</v>
@@ -6839,7 +6839,7 @@
         <v>0</v>
       </c>
       <c r="N145" t="n">
-        <v>2</v>
+        <v>1.987493261455526</v>
       </c>
     </row>
     <row r="146">
@@ -6847,7 +6847,7 @@
         <v>42645</v>
       </c>
       <c r="B146" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C146" t="n">
         <v>3</v>
@@ -6862,16 +6862,16 @@
         <v>2</v>
       </c>
       <c r="G146" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H146" t="n">
-        <v>7.462074620746208</v>
+        <v>8.317519659662242</v>
       </c>
       <c r="I146" t="n">
-        <v>22.38622386223862</v>
+        <v>22.5761247905118</v>
       </c>
       <c r="J146" t="n">
-        <v>79.59546262129288</v>
+        <v>78.42232821967256</v>
       </c>
       <c r="K146" t="n">
         <v>0</v>
@@ -6883,7 +6883,7 @@
         <v>0</v>
       </c>
       <c r="N146" t="n">
-        <v>2</v>
+        <v>1.987493261455526</v>
       </c>
     </row>
     <row r="147">
@@ -6891,7 +6891,7 @@
         <v>42652</v>
       </c>
       <c r="B147" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C147" t="n">
         <v>3</v>
@@ -6906,16 +6906,16 @@
         <v>2</v>
       </c>
       <c r="G147" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H147" t="n">
-        <v>7.462074620746208</v>
+        <v>8.317519659662242</v>
       </c>
       <c r="I147" t="n">
-        <v>22.38622386223862</v>
+        <v>21.38790769627433</v>
       </c>
       <c r="J147" t="n">
-        <v>80.83914172475059</v>
+        <v>80.79876240814748</v>
       </c>
       <c r="K147" t="n">
         <v>0</v>
@@ -6927,7 +6927,7 @@
         <v>0</v>
       </c>
       <c r="N147" t="n">
-        <v>3</v>
+        <v>2.981239892183289</v>
       </c>
     </row>
     <row r="148">
@@ -6935,7 +6935,7 @@
         <v>42659</v>
       </c>
       <c r="B148" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C148" t="n">
         <v>3</v>
@@ -6950,16 +6950,16 @@
         <v>2</v>
       </c>
       <c r="G148" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H148" t="n">
-        <v>8.705753724203909</v>
+        <v>8.317519659662242</v>
       </c>
       <c r="I148" t="n">
-        <v>21.14254475878092</v>
+        <v>22.5761247905118</v>
       </c>
       <c r="J148" t="n">
-        <v>80.83914172475059</v>
+        <v>80.79876240814748</v>
       </c>
       <c r="K148" t="n">
         <v>0</v>
@@ -6971,7 +6971,7 @@
         <v>0</v>
       </c>
       <c r="N148" t="n">
-        <v>2</v>
+        <v>1.987493261455526</v>
       </c>
     </row>
     <row r="149">
@@ -6979,7 +6979,7 @@
         <v>42666</v>
       </c>
       <c r="B149" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C149" t="n">
         <v>3</v>
@@ -6994,16 +6994,16 @@
         <v>2</v>
       </c>
       <c r="G149" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H149" t="n">
-        <v>7.462074620746208</v>
+        <v>8.317519659662242</v>
       </c>
       <c r="I149" t="n">
-        <v>23.62990296569632</v>
+        <v>23.76434188474926</v>
       </c>
       <c r="J149" t="n">
-        <v>82.08282082820828</v>
+        <v>80.79876240814748</v>
       </c>
       <c r="K149" t="n">
         <v>0</v>
@@ -7015,7 +7015,7 @@
         <v>0</v>
       </c>
       <c r="N149" t="n">
-        <v>2</v>
+        <v>1.987493261455526</v>
       </c>
     </row>
     <row r="150">
@@ -7023,10 +7023,10 @@
         <v>42673</v>
       </c>
       <c r="B150" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C150" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D150" t="n">
         <v>3</v>
@@ -7038,16 +7038,16 @@
         <v>2</v>
       </c>
       <c r="G150" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H150" t="n">
-        <v>7.462074620746208</v>
+        <v>7.129302565424778</v>
       </c>
       <c r="I150" t="n">
-        <v>23.62990296569632</v>
+        <v>26.14077607322419</v>
       </c>
       <c r="J150" t="n">
-        <v>75.86442531091978</v>
+        <v>74.85767693696017</v>
       </c>
       <c r="K150" t="n">
         <v>0</v>
@@ -7059,7 +7059,7 @@
         <v>0</v>
       </c>
       <c r="N150" t="n">
-        <v>3</v>
+        <v>2.981239892183289</v>
       </c>
     </row>
     <row r="151">
@@ -7067,7 +7067,7 @@
         <v>42680</v>
       </c>
       <c r="B151" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C151" t="n">
         <v>4</v>
@@ -7082,16 +7082,16 @@
         <v>2</v>
       </c>
       <c r="G151" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H151" t="n">
-        <v>8.705753724203909</v>
+        <v>8.317519659662242</v>
       </c>
       <c r="I151" t="n">
-        <v>21.14254475878092</v>
+        <v>21.38790769627433</v>
       </c>
       <c r="J151" t="n">
-        <v>79.59546262129288</v>
+        <v>78.42232821967256</v>
       </c>
       <c r="K151" t="n">
         <v>0</v>
@@ -7103,7 +7103,7 @@
         <v>0</v>
       </c>
       <c r="N151" t="n">
-        <v>3</v>
+        <v>2.981239892183289</v>
       </c>
     </row>
     <row r="152">
@@ -7126,16 +7126,16 @@
         <v>2</v>
       </c>
       <c r="G152" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H152" t="n">
-        <v>7.462074620746208</v>
+        <v>7.129302565424778</v>
       </c>
       <c r="I152" t="n">
-        <v>22.38622386223862</v>
+        <v>21.38790769627433</v>
       </c>
       <c r="J152" t="n">
-        <v>75.86442531091978</v>
+        <v>79.61054531391002</v>
       </c>
       <c r="K152" t="n">
         <v>0</v>
@@ -7147,7 +7147,7 @@
         <v>0</v>
       </c>
       <c r="N152" t="n">
-        <v>3</v>
+        <v>2.981239892183289</v>
       </c>
     </row>
     <row r="153">
@@ -7155,7 +7155,7 @@
         <v>42694</v>
       </c>
       <c r="B153" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C153" t="n">
         <v>4</v>
@@ -7170,16 +7170,16 @@
         <v>2</v>
       </c>
       <c r="G153" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H153" t="n">
-        <v>7.462074620746208</v>
+        <v>7.129302565424778</v>
       </c>
       <c r="I153" t="n">
-        <v>19.89886565532322</v>
+        <v>20.19969060203687</v>
       </c>
       <c r="J153" t="n">
-        <v>80.83914172475059</v>
+        <v>76.04589403119763</v>
       </c>
       <c r="K153" t="n">
         <v>0</v>
@@ -7191,7 +7191,7 @@
         <v>0</v>
       </c>
       <c r="N153" t="n">
-        <v>3</v>
+        <v>2.981239892183289</v>
       </c>
     </row>
     <row r="154">
@@ -7199,7 +7199,7 @@
         <v>42701</v>
       </c>
       <c r="B154" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C154" t="n">
         <v>4</v>
@@ -7214,16 +7214,16 @@
         <v>2</v>
       </c>
       <c r="G154" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H154" t="n">
-        <v>7.462074620746208</v>
+        <v>7.129302565424778</v>
       </c>
       <c r="I154" t="n">
-        <v>19.89886565532322</v>
+        <v>21.38790769627433</v>
       </c>
       <c r="J154" t="n">
-        <v>75.86442531091978</v>
+        <v>76.04589403119763</v>
       </c>
       <c r="K154" t="n">
         <v>0</v>
@@ -7235,7 +7235,7 @@
         <v>0</v>
       </c>
       <c r="N154" t="n">
-        <v>3</v>
+        <v>2.981239892183289</v>
       </c>
     </row>
     <row r="155">
@@ -7243,7 +7243,7 @@
         <v>42708</v>
       </c>
       <c r="B155" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C155" t="n">
         <v>4</v>
@@ -7258,16 +7258,16 @@
         <v>2</v>
       </c>
       <c r="G155" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H155" t="n">
-        <v>7.462074620746208</v>
+        <v>7.129302565424778</v>
       </c>
       <c r="I155" t="n">
-        <v>23.62990296569632</v>
+        <v>26.14077607322419</v>
       </c>
       <c r="J155" t="n">
-        <v>89.54489544895449</v>
+        <v>89.11628206780972</v>
       </c>
       <c r="K155" t="n">
         <v>0</v>
@@ -7279,7 +7279,7 @@
         <v>0</v>
       </c>
       <c r="N155" t="n">
-        <v>3</v>
+        <v>2.981239892183289</v>
       </c>
     </row>
     <row r="156">
@@ -7293,7 +7293,7 @@
         <v>3</v>
       </c>
       <c r="D156" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E156" t="n">
         <v>6</v>
@@ -7302,16 +7302,16 @@
         <v>2</v>
       </c>
       <c r="G156" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H156" t="n">
-        <v>7.462074620746208</v>
+        <v>7.129302565424778</v>
       </c>
       <c r="I156" t="n">
-        <v>21.14254475878092</v>
+        <v>20.19969060203687</v>
       </c>
       <c r="J156" t="n">
-        <v>73.37706710400437</v>
+        <v>70.10480856001031</v>
       </c>
       <c r="K156" t="n">
         <v>0</v>
@@ -7323,7 +7323,7 @@
         <v>0</v>
       </c>
       <c r="N156" t="n">
-        <v>2</v>
+        <v>2.981239892183289</v>
       </c>
     </row>
     <row r="157">
@@ -7346,16 +7346,16 @@
         <v>2</v>
       </c>
       <c r="G157" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H157" t="n">
-        <v>7.462074620746208</v>
+        <v>7.129302565424778</v>
       </c>
       <c r="I157" t="n">
-        <v>23.62990296569632</v>
+        <v>22.5761247905118</v>
       </c>
       <c r="J157" t="n">
-        <v>72.13338800054667</v>
+        <v>68.91659146577285</v>
       </c>
       <c r="K157" t="n">
         <v>0</v>
@@ -7367,7 +7367,7 @@
         <v>0</v>
       </c>
       <c r="N157" t="n">
-        <v>3</v>
+        <v>2.981239892183289</v>
       </c>
     </row>
     <row r="158">
@@ -7390,16 +7390,16 @@
         <v>2</v>
       </c>
       <c r="G158" t="n">
-        <v>1.243679103457701</v>
+        <v>1.188217094237463</v>
       </c>
       <c r="H158" t="n">
-        <v>6.218395517288506</v>
+        <v>7.129302565424778</v>
       </c>
       <c r="I158" t="n">
-        <v>27.36094027606943</v>
+        <v>28.51721026169911</v>
       </c>
       <c r="J158" t="n">
-        <v>69.64602979363127</v>
+        <v>70.10480856001031</v>
       </c>
       <c r="K158" t="n">
         <v>0</v>
@@ -7411,7 +7411,7 @@
         <v>0</v>
       </c>
       <c r="N158" t="n">
-        <v>2</v>
+        <v>1.987493261455526</v>
       </c>
     </row>
   </sheetData>
